--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-24.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1067"/>
+  <dimension ref="A1:G950"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21974,16 +21974,20 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>2025-03-05 00:50:00+05:30</t>
+          <t>2025-03-05 03:00:00+05:30</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>Fed Williams Speech</t>
+          <t>API Crude Oil Stock ChangeFEB/28</t>
         </is>
       </c>
       <c r="C744" t="inlineStr"/>
-      <c r="D744" t="inlineStr"/>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>-0.640M</t>
+        </is>
+      </c>
       <c r="E744" t="inlineStr"/>
       <c r="F744" t="inlineStr"/>
       <c r="G744" t="n">
@@ -22001,13 +22005,21 @@
           <t>API Crude Oil Stock ChangeFEB/28</t>
         </is>
       </c>
-      <c r="C745" t="inlineStr"/>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>-1.455M</t>
+        </is>
+      </c>
       <c r="D745" t="inlineStr">
         <is>
           <t>-0.640M</t>
         </is>
       </c>
-      <c r="E745" t="inlineStr"/>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>-0.3M</t>
+        </is>
+      </c>
       <c r="F745" t="inlineStr"/>
       <c r="G745" t="n">
         <v>2</v>
@@ -22016,29 +22028,21 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>2025-03-05 03:00:00+05:30</t>
+          <t>2025-03-05 17:30:00+05:30</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>API Crude Oil Stock ChangeFEB/28</t>
-        </is>
-      </c>
-      <c r="C746" t="inlineStr">
-        <is>
-          <t>-1.455M</t>
-        </is>
-      </c>
+          <t>MBA 30-Year Mortgage RateFEB/28</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr"/>
       <c r="D746" t="inlineStr">
         <is>
-          <t>-0.640M</t>
-        </is>
-      </c>
-      <c r="E746" t="inlineStr">
-        <is>
-          <t>-0.3M</t>
-        </is>
-      </c>
+          <t>6.88%</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr"/>
       <c r="F746" t="inlineStr"/>
       <c r="G746" t="n">
         <v>2</v>
@@ -22052,19 +22056,19 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/28</t>
+          <t>MBA Mortgage Market IndexFEB/28</t>
         </is>
       </c>
       <c r="C747" t="inlineStr"/>
       <c r="D747" t="inlineStr">
         <is>
-          <t>6.88%</t>
+          <t>212.3</t>
         </is>
       </c>
       <c r="E747" t="inlineStr"/>
       <c r="F747" t="inlineStr"/>
       <c r="G747" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="748">
@@ -22075,13 +22079,13 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/28</t>
+          <t>MBA Purchase IndexFEB/28</t>
         </is>
       </c>
       <c r="C748" t="inlineStr"/>
       <c r="D748" t="inlineStr">
         <is>
-          <t>212.3</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="E748" t="inlineStr"/>
@@ -22098,13 +22102,13 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/28</t>
+          <t>MBA Mortgage Refinance IndexFEB/28</t>
         </is>
       </c>
       <c r="C749" t="inlineStr"/>
       <c r="D749" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>572.5</t>
         </is>
       </c>
       <c r="E749" t="inlineStr"/>
@@ -22121,13 +22125,13 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/28</t>
+          <t>MBA Mortgage ApplicationsFEB/28</t>
         </is>
       </c>
       <c r="C750" t="inlineStr"/>
       <c r="D750" t="inlineStr">
         <is>
-          <t>572.5</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="E750" t="inlineStr"/>
@@ -22144,19 +22148,23 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/28</t>
-        </is>
-      </c>
-      <c r="C751" t="inlineStr"/>
+          <t>MBA 30-Year Mortgage RateFEB/28</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>6.73%</t>
+        </is>
+      </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>6.88%</t>
         </is>
       </c>
       <c r="E751" t="inlineStr"/>
       <c r="F751" t="inlineStr"/>
       <c r="G751" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="752">
@@ -22167,23 +22175,23 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/28</t>
+          <t>MBA Mortgage ApplicationsFEB/28</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
         <is>
-          <t>6.73%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>6.88%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="E752" t="inlineStr"/>
       <c r="F752" t="inlineStr"/>
       <c r="G752" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="753">
@@ -22194,17 +22202,17 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/28</t>
+          <t>MBA Mortgage Market IndexFEB/28</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>242.2</t>
         </is>
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>212.3</t>
         </is>
       </c>
       <c r="E753" t="inlineStr"/>
@@ -22221,17 +22229,17 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/28</t>
+          <t>MBA Purchase IndexFEB/28</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
         <is>
-          <t>242.2</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>212.3</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="E754" t="inlineStr"/>
@@ -22248,17 +22256,17 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/28</t>
+          <t>MBA Mortgage Refinance IndexFEB/28</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>784.2</t>
         </is>
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>572.5</t>
         </is>
       </c>
       <c r="E755" t="inlineStr"/>
@@ -22270,28 +22278,36 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>2025-03-05 17:30:00+05:30</t>
+          <t>2025-03-05 18:45:00+05:30</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/28</t>
+          <t>ADP Employment ChangeFEB</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>784.2</t>
+          <t>77K</t>
         </is>
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>572.5</t>
-        </is>
-      </c>
-      <c r="E756" t="inlineStr"/>
-      <c r="F756" t="inlineStr"/>
+          <t>186K</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>140K</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>160.0K</t>
+        </is>
+      </c>
       <c r="G756" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="757">
@@ -22305,14 +22321,10 @@
           <t>ADP Employment ChangeFEB</t>
         </is>
       </c>
-      <c r="C757" t="inlineStr">
-        <is>
-          <t>77K</t>
-        </is>
-      </c>
+      <c r="C757" t="inlineStr"/>
       <c r="D757" t="inlineStr">
         <is>
-          <t>186K</t>
+          <t>183K</t>
         </is>
       </c>
       <c r="E757" t="inlineStr">
@@ -22332,28 +22344,28 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>2025-03-05 18:45:00+05:30</t>
+          <t>2025-03-05 20:15:00+05:30</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>ADP Employment ChangeFEB</t>
+          <t>S&amp;P Global Composite PMI FinalFEB</t>
         </is>
       </c>
       <c r="C758" t="inlineStr"/>
       <c r="D758" t="inlineStr">
         <is>
-          <t>183K</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>140K</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="F758" t="inlineStr">
         <is>
-          <t>160.0K</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G758" t="n">
@@ -22368,23 +22380,23 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FinalFEB</t>
+          <t>S&amp;P Global Services PMI FinalFEB</t>
         </is>
       </c>
       <c r="C759" t="inlineStr"/>
       <c r="D759" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="F759" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="G759" t="n">
@@ -22394,94 +22406,82 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>2025-03-05 20:15:00+05:30</t>
+          <t>2025-03-05 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FinalFEB</t>
+          <t>ISM Services New OrdersFEB</t>
         </is>
       </c>
       <c r="C760" t="inlineStr"/>
       <c r="D760" t="inlineStr">
         <is>
-          <t>52.9</t>
-        </is>
-      </c>
-      <c r="E760" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
+          <t>51.3</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr"/>
       <c r="F760" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="G760" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>2025-03-05 20:15:00+05:30</t>
+          <t>2025-03-05 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FinalFEB</t>
+          <t>ISM Services EmploymentFEB</t>
         </is>
       </c>
       <c r="C761" t="inlineStr"/>
       <c r="D761" t="inlineStr">
         <is>
-          <t>52.7</t>
-        </is>
-      </c>
-      <c r="E761" t="inlineStr">
-        <is>
-          <t>50.4</t>
-        </is>
-      </c>
+          <t>52.3</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr"/>
       <c r="F761" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="G761" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>2025-03-05 20:15:00+05:30</t>
+          <t>2025-03-05 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FinalFEB</t>
+          <t>ISM Services Business ActivityFEB</t>
         </is>
       </c>
       <c r="C762" t="inlineStr"/>
       <c r="D762" t="inlineStr">
         <is>
-          <t>52.9</t>
-        </is>
-      </c>
-      <c r="E762" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
+          <t>54.5</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr"/>
       <c r="F762" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="G762" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="763">
@@ -22492,27 +22492,23 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>Factory Orders MoMJAN</t>
+          <t>Factory Orders ex TransportationJAN</t>
         </is>
       </c>
       <c r="C763" t="inlineStr"/>
       <c r="D763" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="E763" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr"/>
       <c r="F763" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G763" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="764">
@@ -22523,23 +22519,27 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationJAN</t>
+          <t>Factory Orders MoMJAN</t>
         </is>
       </c>
       <c r="C764" t="inlineStr"/>
       <c r="D764" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E764" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F764" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="G764" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="765">
@@ -22550,23 +22550,23 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityFEB</t>
+          <t>ISM Services PMIFEB</t>
         </is>
       </c>
       <c r="C765" t="inlineStr"/>
       <c r="D765" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E765" t="inlineStr"/>
       <c r="F765" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G765" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="766">
@@ -22577,19 +22577,23 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentFEB</t>
+          <t>ISM Services PricesFEB</t>
         </is>
       </c>
       <c r="C766" t="inlineStr"/>
       <c r="D766" t="inlineStr">
         <is>
-          <t>52.3</t>
-        </is>
-      </c>
-      <c r="E766" t="inlineStr"/>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
       <c r="F766" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="G766" t="n">
@@ -22599,57 +22603,49 @@
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>2025-03-05 20:30:00+05:30</t>
+          <t>2025-03-05 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersFEB</t>
+          <t>EIA Gasoline Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C767" t="inlineStr"/>
       <c r="D767" t="inlineStr">
         <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="E767" t="inlineStr"/>
-      <c r="F767" t="inlineStr">
-        <is>
-          <t>51.2</t>
-        </is>
-      </c>
+          <t>0.369M</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>-1M</t>
+        </is>
+      </c>
+      <c r="F767" t="inlineStr"/>
       <c r="G767" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>2025-03-05 20:30:00+05:30</t>
+          <t>2025-03-05 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>ISM Services PricesFEB</t>
+          <t>EIA Crude Oil Imports ChangeFEB/28</t>
         </is>
       </c>
       <c r="C768" t="inlineStr"/>
       <c r="D768" t="inlineStr">
         <is>
-          <t>60.4</t>
-        </is>
-      </c>
-      <c r="E768" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="F768" t="inlineStr">
-        <is>
-          <t>60.6</t>
-        </is>
-      </c>
+          <t>0.292M</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr"/>
+      <c r="F768" t="inlineStr"/>
       <c r="G768" t="n">
         <v>3</v>
       </c>
@@ -22657,57 +22653,49 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>2025-03-05 20:30:00+05:30</t>
+          <t>2025-03-05 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>ISM Services PMIFEB</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C769" t="inlineStr"/>
       <c r="D769" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="E769" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="F769" t="inlineStr">
-        <is>
-          <t>52.7</t>
-        </is>
-      </c>
+          <t>1.282M</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr"/>
+      <c r="F769" t="inlineStr"/>
       <c r="G769" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>2025-03-05 20:30:00+05:30</t>
+          <t>2025-03-05 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersFEB</t>
+          <t>EIA Distillate Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C770" t="inlineStr"/>
       <c r="D770" t="inlineStr">
         <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="E770" t="inlineStr"/>
-      <c r="F770" t="inlineStr">
-        <is>
-          <t>51.2</t>
-        </is>
-      </c>
+          <t>3.908M</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>-0.3M</t>
+        </is>
+      </c>
+      <c r="F770" t="inlineStr"/>
       <c r="G770" t="n">
         <v>3</v>
       </c>
@@ -22715,26 +22703,22 @@
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>2025-03-05 20:30:00+05:30</t>
+          <t>2025-03-05 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentFEB</t>
+          <t>EIA Gasoline Production ChangeFEB/28</t>
         </is>
       </c>
       <c r="C771" t="inlineStr"/>
       <c r="D771" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>-0.02M</t>
         </is>
       </c>
       <c r="E771" t="inlineStr"/>
-      <c r="F771" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
+      <c r="F771" t="inlineStr"/>
       <c r="G771" t="n">
         <v>3</v>
       </c>
@@ -22742,26 +22726,22 @@
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>2025-03-05 20:30:00+05:30</t>
+          <t>2025-03-05 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityFEB</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C772" t="inlineStr"/>
       <c r="D772" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>0.134M</t>
         </is>
       </c>
       <c r="E772" t="inlineStr"/>
-      <c r="F772" t="inlineStr">
-        <is>
-          <t>54.2</t>
-        </is>
-      </c>
+      <c r="F772" t="inlineStr"/>
       <c r="G772" t="n">
         <v>3</v>
       </c>
@@ -22769,26 +22749,22 @@
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>2025-03-05 20:30:00+05:30</t>
+          <t>2025-03-05 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationJAN</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/28</t>
         </is>
       </c>
       <c r="C773" t="inlineStr"/>
       <c r="D773" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.317M</t>
         </is>
       </c>
       <c r="E773" t="inlineStr"/>
-      <c r="F773" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="F773" t="inlineStr"/>
       <c r="G773" t="n">
         <v>3</v>
       </c>
@@ -22796,30 +22772,26 @@
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>2025-03-05 20:30:00+05:30</t>
+          <t>2025-03-05 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>Factory Orders MoMJAN</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C774" t="inlineStr"/>
       <c r="D774" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-2.332M</t>
         </is>
       </c>
       <c r="E774" t="inlineStr">
         <is>
-          <t>1.6%</t>
-        </is>
-      </c>
-      <c r="F774" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
+          <t>0.9M</t>
+        </is>
+      </c>
+      <c r="F774" t="inlineStr"/>
       <c r="G774" t="n">
         <v>2</v>
       </c>
@@ -22827,57 +22799,45 @@
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>2025-03-05 20:30:00+05:30</t>
+          <t>2025-03-05 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>ISM Services PMIFEB</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/28</t>
         </is>
       </c>
       <c r="C775" t="inlineStr"/>
       <c r="D775" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>0.439M</t>
         </is>
       </c>
       <c r="E775" t="inlineStr"/>
-      <c r="F775" t="inlineStr">
-        <is>
-          <t>52.7</t>
-        </is>
-      </c>
+      <c r="F775" t="inlineStr"/>
       <c r="G775" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>2025-03-05 20:30:00+05:30</t>
+          <t>2025-03-05 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>ISM Services PricesFEB</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C776" t="inlineStr"/>
       <c r="D776" t="inlineStr">
         <is>
-          <t>60.4</t>
-        </is>
-      </c>
-      <c r="E776" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="F776" t="inlineStr">
-        <is>
-          <t>60.6</t>
-        </is>
-      </c>
+          <t>4.200%</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr"/>
+      <c r="F776" t="inlineStr"/>
       <c r="G776" t="n">
         <v>3</v>
       </c>
@@ -22885,25 +22845,21 @@
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>2025-03-05 21:00:00+05:30</t>
+          <t>2025-03-05 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/28</t>
+          <t>Total Vehicle SalesFEB</t>
         </is>
       </c>
       <c r="C777" t="inlineStr"/>
       <c r="D777" t="inlineStr">
         <is>
-          <t>3.908M</t>
-        </is>
-      </c>
-      <c r="E777" t="inlineStr">
-        <is>
-          <t>0.87M</t>
-        </is>
-      </c>
+          <t>15.6M</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr"/>
       <c r="F777" t="inlineStr"/>
       <c r="G777" t="n">
         <v>3</v>
@@ -22912,20 +22868,16 @@
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>2025-03-05 21:00:00+05:30</t>
+          <t>2025-03-06 00:30:00+05:30</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/28</t>
+          <t>Fed Beige Book</t>
         </is>
       </c>
       <c r="C778" t="inlineStr"/>
-      <c r="D778" t="inlineStr">
-        <is>
-          <t>0.292M</t>
-        </is>
-      </c>
+      <c r="D778" t="inlineStr"/>
       <c r="E778" t="inlineStr"/>
       <c r="F778" t="inlineStr"/>
       <c r="G778" t="n">
@@ -22935,72 +22887,84 @@
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>2025-03-05 21:00:00+05:30</t>
+          <t>2025-03-06 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/28</t>
+          <t>Challenger Job CutsFEB</t>
         </is>
       </c>
       <c r="C779" t="inlineStr"/>
       <c r="D779" t="inlineStr">
         <is>
-          <t>0.369M</t>
-        </is>
-      </c>
-      <c r="E779" t="inlineStr">
-        <is>
-          <t>0.13M</t>
-        </is>
-      </c>
-      <c r="F779" t="inlineStr"/>
+          <t>49.795K</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr"/>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>56.0K</t>
+        </is>
+      </c>
       <c r="G779" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>2025-03-05 21:00:00+05:30</t>
+          <t>2025-03-06 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/28</t>
+          <t>ExportsJAN</t>
         </is>
       </c>
       <c r="C780" t="inlineStr"/>
       <c r="D780" t="inlineStr">
         <is>
-          <t>1.282M</t>
+          <t>$266.5B</t>
         </is>
       </c>
       <c r="E780" t="inlineStr"/>
-      <c r="F780" t="inlineStr"/>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>$273.0B</t>
+        </is>
+      </c>
       <c r="G780" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>2025-03-05 21:00:00+05:30</t>
+          <t>2025-03-06 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/28</t>
+          <t>Continuing Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C781" t="inlineStr"/>
       <c r="D781" t="inlineStr">
         <is>
-          <t>-0.02M</t>
-        </is>
-      </c>
-      <c r="E781" t="inlineStr"/>
-      <c r="F781" t="inlineStr"/>
+          <t>1862K</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>1880K</t>
+        </is>
+      </c>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>1870.0K</t>
+        </is>
+      </c>
       <c r="G781" t="n">
         <v>3</v>
       </c>
@@ -23008,49 +22972,57 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>2025-03-05 21:00:00+05:30</t>
+          <t>2025-03-06 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/28</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="C782" t="inlineStr"/>
       <c r="D782" t="inlineStr">
         <is>
-          <t>0.134M</t>
+          <t>$364.9B</t>
         </is>
       </c>
       <c r="E782" t="inlineStr"/>
-      <c r="F782" t="inlineStr"/>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>$396.0B</t>
+        </is>
+      </c>
       <c r="G782" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>2025-03-05 21:00:00+05:30</t>
+          <t>2025-03-06 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/28</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="C783" t="inlineStr"/>
       <c r="D783" t="inlineStr">
         <is>
-          <t>-2.332M</t>
+          <t>$-98.4B</t>
         </is>
       </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t>-0.29M</t>
-        </is>
-      </c>
-      <c r="F783" t="inlineStr"/>
+          <t>$-127.4B</t>
+        </is>
+      </c>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>$-123B</t>
+        </is>
+      </c>
       <c r="G783" t="n">
         <v>2</v>
       </c>
@@ -23058,22 +23030,26 @@
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>2025-03-05 21:00:00+05:30</t>
+          <t>2025-03-06 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/28</t>
+          <t>Jobless Claims 4-week AverageMAR/01</t>
         </is>
       </c>
       <c r="C784" t="inlineStr"/>
       <c r="D784" t="inlineStr">
         <is>
-          <t>0.317M</t>
+          <t>224K</t>
         </is>
       </c>
       <c r="E784" t="inlineStr"/>
-      <c r="F784" t="inlineStr"/>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>226.0K</t>
+        </is>
+      </c>
       <c r="G784" t="n">
         <v>3</v>
       </c>
@@ -23081,49 +23057,61 @@
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>2025-03-05 21:00:00+05:30</t>
+          <t>2025-03-06 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/28</t>
+          <t>Unit Labour Costs QoQ FinalQ4</t>
         </is>
       </c>
       <c r="C785" t="inlineStr"/>
       <c r="D785" t="inlineStr">
         <is>
-          <t>0.369M</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E785" t="inlineStr">
         <is>
-          <t>-1M</t>
-        </is>
-      </c>
-      <c r="F785" t="inlineStr"/>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>3.0%</t>
+        </is>
+      </c>
       <c r="G785" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>2025-03-05 21:00:00+05:30</t>
+          <t>2025-03-06 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/28</t>
+          <t>Nonfarm Productivity QoQ FinalQ4</t>
         </is>
       </c>
       <c r="C786" t="inlineStr"/>
       <c r="D786" t="inlineStr">
         <is>
-          <t>0.292M</t>
-        </is>
-      </c>
-      <c r="E786" t="inlineStr"/>
-      <c r="F786" t="inlineStr"/>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>1.2%</t>
+        </is>
+      </c>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>1.2%</t>
+        </is>
+      </c>
       <c r="G786" t="n">
         <v>3</v>
       </c>
@@ -23131,45 +23119,61 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>2025-03-05 21:00:00+05:30</t>
+          <t>2025-03-06 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/28</t>
+          <t>Initial Jobless ClaimsMAR/01</t>
         </is>
       </c>
       <c r="C787" t="inlineStr"/>
       <c r="D787" t="inlineStr">
         <is>
-          <t>1.282M</t>
-        </is>
-      </c>
-      <c r="E787" t="inlineStr"/>
-      <c r="F787" t="inlineStr"/>
+          <t>242K</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>235K</t>
+        </is>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>250.0K</t>
+        </is>
+      </c>
       <c r="G787" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>2025-03-05 21:00:00+05:30</t>
+          <t>2025-03-06 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/28</t>
+          <t>Wholesale Inventories MoMJAN</t>
         </is>
       </c>
       <c r="C788" t="inlineStr"/>
       <c r="D788" t="inlineStr">
         <is>
-          <t>0.439M</t>
-        </is>
-      </c>
-      <c r="E788" t="inlineStr"/>
-      <c r="F788" t="inlineStr"/>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="G788" t="n">
         <v>3</v>
       </c>
@@ -23177,23 +23181,23 @@
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>2025-03-05 21:00:00+05:30</t>
+          <t>2025-03-06 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/28</t>
+          <t>EIA Natural Gas Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C789" t="inlineStr"/>
       <c r="D789" t="inlineStr">
         <is>
-          <t>3.908M</t>
+          <t>-261Bcf</t>
         </is>
       </c>
       <c r="E789" t="inlineStr">
         <is>
-          <t>-0.3M</t>
+          <t>-96Bcf</t>
         </is>
       </c>
       <c r="F789" t="inlineStr"/>
@@ -23204,18 +23208,18 @@
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>2025-03-05 21:00:00+05:30</t>
+          <t>2025-03-06 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/28</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C790" t="inlineStr"/>
       <c r="D790" t="inlineStr">
         <is>
-          <t>-0.02M</t>
+          <t>4.235%</t>
         </is>
       </c>
       <c r="E790" t="inlineStr"/>
@@ -23227,18 +23231,18 @@
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>2025-03-05 21:00:00+05:30</t>
+          <t>2025-03-06 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/28</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C791" t="inlineStr"/>
       <c r="D791" t="inlineStr">
         <is>
-          <t>0.134M</t>
+          <t>4.235%</t>
         </is>
       </c>
       <c r="E791" t="inlineStr"/>
@@ -23250,18 +23254,18 @@
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>2025-03-05 21:00:00+05:30</t>
+          <t>2025-03-06 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/28</t>
+          <t>15-Year Mortgage RateMAR/06</t>
         </is>
       </c>
       <c r="C792" t="inlineStr"/>
       <c r="D792" t="inlineStr">
         <is>
-          <t>0.317M</t>
+          <t>5.94%</t>
         </is>
       </c>
       <c r="E792" t="inlineStr"/>
@@ -23273,70 +23277,58 @@
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>2025-03-05 21:00:00+05:30</t>
+          <t>2025-03-06 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/28</t>
+          <t>30-Year Mortgage RateMAR/06</t>
         </is>
       </c>
       <c r="C793" t="inlineStr"/>
       <c r="D793" t="inlineStr">
         <is>
-          <t>-2.332M</t>
-        </is>
-      </c>
-      <c r="E793" t="inlineStr">
-        <is>
-          <t>0.9M</t>
-        </is>
-      </c>
+          <t>6.76%</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr"/>
       <c r="F793" t="inlineStr"/>
       <c r="G793" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>2025-03-05 21:00:00+05:30</t>
+          <t>2025-03-07 02:00:00+05:30</t>
         </is>
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/28</t>
+          <t>Fed Waller Speech</t>
         </is>
       </c>
       <c r="C794" t="inlineStr"/>
-      <c r="D794" t="inlineStr">
-        <is>
-          <t>0.439M</t>
-        </is>
-      </c>
+      <c r="D794" t="inlineStr"/>
       <c r="E794" t="inlineStr"/>
       <c r="F794" t="inlineStr"/>
       <c r="G794" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>2025-03-05 22:00:00+05:30</t>
+          <t>2025-03-07 03:00:00+05:30</t>
         </is>
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>Fed Balance SheetMAR/05</t>
         </is>
       </c>
       <c r="C795" t="inlineStr"/>
-      <c r="D795" t="inlineStr">
-        <is>
-          <t>4.200%</t>
-        </is>
-      </c>
+      <c r="D795" t="inlineStr"/>
       <c r="E795" t="inlineStr"/>
       <c r="F795" t="inlineStr"/>
       <c r="G795" t="n">
@@ -23346,41 +23338,37 @@
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>2025-03-05 22:00:00+05:30</t>
+          <t>2025-03-07 05:30:00+05:30</t>
         </is>
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesFEB</t>
+          <t>Fed Bostic Speech</t>
         </is>
       </c>
       <c r="C796" t="inlineStr"/>
-      <c r="D796" t="inlineStr">
-        <is>
-          <t>15.6M</t>
-        </is>
-      </c>
+      <c r="D796" t="inlineStr"/>
       <c r="E796" t="inlineStr"/>
       <c r="F796" t="inlineStr"/>
       <c r="G796" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>2025-03-05 22:00:00+05:30</t>
+          <t>2025-03-07 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>Used Car Prices YoYFEB</t>
         </is>
       </c>
       <c r="C797" t="inlineStr"/>
       <c r="D797" t="inlineStr">
         <is>
-          <t>4.200%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="E797" t="inlineStr"/>
@@ -23392,18 +23380,18 @@
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>2025-03-05 22:00:00+05:30</t>
+          <t>2025-03-07 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesFEB</t>
+          <t>Used Car Prices MoMFEB</t>
         </is>
       </c>
       <c r="C798" t="inlineStr"/>
       <c r="D798" t="inlineStr">
         <is>
-          <t>15.6M</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E798" t="inlineStr"/>
@@ -23415,37 +23403,57 @@
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>2025-03-06 00:30:00+05:30</t>
+          <t>2025-03-07 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>Fed Beige Book</t>
+          <t>Non Farm PayrollsFEB</t>
         </is>
       </c>
       <c r="C799" t="inlineStr"/>
-      <c r="D799" t="inlineStr"/>
-      <c r="E799" t="inlineStr"/>
-      <c r="F799" t="inlineStr"/>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>143K</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>160K</t>
+        </is>
+      </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>150.0K</t>
+        </is>
+      </c>
       <c r="G799" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>2025-03-06 00:30:00+05:30</t>
+          <t>2025-03-07 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>Fed Beige Book</t>
+          <t>Government PayrollsFEB</t>
         </is>
       </c>
       <c r="C800" t="inlineStr"/>
-      <c r="D800" t="inlineStr"/>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>32K</t>
+        </is>
+      </c>
       <c r="E800" t="inlineStr"/>
-      <c r="F800" t="inlineStr"/>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>-20.0K</t>
+        </is>
+      </c>
       <c r="G800" t="n">
         <v>3</v>
       </c>
@@ -23453,24 +23461,28 @@
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>2025-03-06 18:00:00+05:30</t>
+          <t>2025-03-07 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>Challenger Job CutsFEB</t>
+          <t>Nonfarm Payrolls PrivateFEB</t>
         </is>
       </c>
       <c r="C801" t="inlineStr"/>
       <c r="D801" t="inlineStr">
         <is>
-          <t>49.795K</t>
-        </is>
-      </c>
-      <c r="E801" t="inlineStr"/>
+          <t>111K</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>143K</t>
+        </is>
+      </c>
       <c r="F801" t="inlineStr">
         <is>
-          <t>56.0K</t>
+          <t>170.0K</t>
         </is>
       </c>
       <c r="G801" t="n">
@@ -23480,51 +23492,59 @@
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>2025-03-06 18:00:00+05:30</t>
+          <t>2025-03-07 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>Challenger Job CutsFEB</t>
+          <t>Unemployment RateFEB</t>
         </is>
       </c>
       <c r="C802" t="inlineStr"/>
       <c r="D802" t="inlineStr">
         <is>
-          <t>49.795K</t>
-        </is>
-      </c>
-      <c r="E802" t="inlineStr"/>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
       <c r="F802" t="inlineStr">
         <is>
-          <t>56.0K</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G802" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>2025-03-06 19:00:00+05:30</t>
+          <t>2025-03-07 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>ExportsJAN</t>
+          <t>Average Hourly Earnings MoMFEB</t>
         </is>
       </c>
       <c r="C803" t="inlineStr"/>
       <c r="D803" t="inlineStr">
         <is>
-          <t>$266.5B</t>
-        </is>
-      </c>
-      <c r="E803" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F803" t="inlineStr">
         <is>
-          <t>$273.0B</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G803" t="n">
@@ -23534,28 +23554,28 @@
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>2025-03-06 19:00:00+05:30</t>
+          <t>2025-03-07 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Average Hourly Earnings YoYFEB</t>
         </is>
       </c>
       <c r="C804" t="inlineStr"/>
       <c r="D804" t="inlineStr">
         <is>
-          <t>$-98.4B</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="E804" t="inlineStr">
         <is>
-          <t>$-127.4B</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F804" t="inlineStr">
         <is>
-          <t>$-123B</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="G804" t="n">
@@ -23565,173 +23585,153 @@
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>2025-03-06 19:00:00+05:30</t>
+          <t>2025-03-07 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/22</t>
+          <t>Participation RateFEB</t>
         </is>
       </c>
       <c r="C805" t="inlineStr"/>
       <c r="D805" t="inlineStr">
         <is>
-          <t>1862K</t>
-        </is>
-      </c>
-      <c r="E805" t="inlineStr">
-        <is>
-          <t>1880K</t>
-        </is>
-      </c>
+          <t>62.6%</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr"/>
       <c r="F805" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="G805" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>2025-03-06 19:00:00+05:30</t>
+          <t>2025-03-07 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>ExportsJAN</t>
+          <t>Average Weekly HoursFEB</t>
         </is>
       </c>
       <c r="C806" t="inlineStr"/>
       <c r="D806" t="inlineStr">
         <is>
-          <t>$266.5B</t>
-        </is>
-      </c>
-      <c r="E806" t="inlineStr"/>
+          <t>34.1</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>34.2</t>
+        </is>
+      </c>
       <c r="F806" t="inlineStr">
         <is>
-          <t>$273.0B</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="G806" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>2025-03-06 19:00:00+05:30</t>
+          <t>2025-03-07 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>Manufacturing PayrollsFEB</t>
         </is>
       </c>
       <c r="C807" t="inlineStr"/>
       <c r="D807" t="inlineStr">
         <is>
-          <t>$364.9B</t>
-        </is>
-      </c>
-      <c r="E807" t="inlineStr"/>
+          <t>3K</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>5K</t>
+        </is>
+      </c>
       <c r="F807" t="inlineStr">
         <is>
-          <t>$396.0B</t>
+          <t>6.0K</t>
         </is>
       </c>
       <c r="G807" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>2025-03-06 19:00:00+05:30</t>
+          <t>2025-03-07 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsMAR/01</t>
+          <t>U-6 Unemployment RateFEB</t>
         </is>
       </c>
       <c r="C808" t="inlineStr"/>
       <c r="D808" t="inlineStr">
         <is>
-          <t>242K</t>
-        </is>
-      </c>
-      <c r="E808" t="inlineStr">
-        <is>
-          <t>235K</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="E808" t="inlineStr"/>
       <c r="F808" t="inlineStr">
         <is>
-          <t>250.0K</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="G808" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>2025-03-06 19:00:00+05:30</t>
+          <t>2025-03-07 20:45:00+05:30</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/22</t>
+          <t>Fed Bowman Speech</t>
         </is>
       </c>
       <c r="C809" t="inlineStr"/>
-      <c r="D809" t="inlineStr">
-        <is>
-          <t>1862K</t>
-        </is>
-      </c>
-      <c r="E809" t="inlineStr">
-        <is>
-          <t>1880K</t>
-        </is>
-      </c>
-      <c r="F809" t="inlineStr">
-        <is>
-          <t>1870.0K</t>
-        </is>
-      </c>
+      <c r="D809" t="inlineStr"/>
+      <c r="E809" t="inlineStr"/>
+      <c r="F809" t="inlineStr"/>
       <c r="G809" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>2025-03-06 19:00:00+05:30</t>
+          <t>2025-03-07 21:15:00+05:30</t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>Fed Williams Speech</t>
         </is>
       </c>
       <c r="C810" t="inlineStr"/>
-      <c r="D810" t="inlineStr">
-        <is>
-          <t>$364.9B</t>
-        </is>
-      </c>
+      <c r="D810" t="inlineStr"/>
       <c r="E810" t="inlineStr"/>
-      <c r="F810" t="inlineStr">
-        <is>
-          <t>$396.0B</t>
-        </is>
-      </c>
+      <c r="F810" t="inlineStr"/>
       <c r="G810" t="n">
         <v>2</v>
       </c>
@@ -23739,115 +23739,83 @@
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>2025-03-06 19:00:00+05:30</t>
+          <t>2025-03-07 22:50:00+05:30</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageMAR/01</t>
+          <t>Fed Kugler Speech</t>
         </is>
       </c>
       <c r="C811" t="inlineStr"/>
-      <c r="D811" t="inlineStr">
-        <is>
-          <t>224K</t>
-        </is>
-      </c>
+      <c r="D811" t="inlineStr"/>
       <c r="E811" t="inlineStr"/>
-      <c r="F811" t="inlineStr">
-        <is>
-          <t>226.0K</t>
-        </is>
-      </c>
+      <c r="F811" t="inlineStr"/>
       <c r="G811" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>2025-03-06 19:00:00+05:30</t>
+          <t>2025-03-07 23:00:00+05:30</t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ FinalQ4</t>
+          <t>Fed Chair Powell Speech</t>
         </is>
       </c>
       <c r="C812" t="inlineStr"/>
-      <c r="D812" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E812" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="F812" t="inlineStr">
-        <is>
-          <t>3.0%</t>
-        </is>
-      </c>
+      <c r="D812" t="inlineStr"/>
+      <c r="E812" t="inlineStr"/>
+      <c r="F812" t="inlineStr"/>
       <c r="G812" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>2025-03-06 19:00:00+05:30</t>
+          <t>2025-03-07 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Used Car Prices YoYFEB</t>
         </is>
       </c>
       <c r="C813" t="inlineStr"/>
       <c r="D813" t="inlineStr">
         <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
-      <c r="E813" t="inlineStr">
-        <is>
-          <t>$-127.4B</t>
-        </is>
-      </c>
-      <c r="F813" t="inlineStr">
-        <is>
-          <t>$-123B</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr"/>
+      <c r="F813" t="inlineStr"/>
       <c r="G813" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>2025-03-06 19:00:00+05:30</t>
+          <t>2025-03-07 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageMAR/01</t>
+          <t>Used Car Prices MoMFEB</t>
         </is>
       </c>
       <c r="C814" t="inlineStr"/>
       <c r="D814" t="inlineStr">
         <is>
-          <t>224K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E814" t="inlineStr"/>
-      <c r="F814" t="inlineStr">
-        <is>
-          <t>226.0K</t>
-        </is>
-      </c>
+      <c r="F814" t="inlineStr"/>
       <c r="G814" t="n">
         <v>3</v>
       </c>
@@ -23855,30 +23823,22 @@
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>2025-03-06 19:00:00+05:30</t>
+          <t>2025-03-07 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ FinalQ4</t>
+          <t>Baker Hughes Oil Rig CountMAR/07</t>
         </is>
       </c>
       <c r="C815" t="inlineStr"/>
       <c r="D815" t="inlineStr">
         <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="E815" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
-      <c r="F815" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
+          <t>489</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr"/>
+      <c r="F815" t="inlineStr"/>
       <c r="G815" t="n">
         <v>3</v>
       </c>
@@ -23886,61 +23846,41 @@
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>2025-03-06 19:00:00+05:30</t>
+          <t>2025-03-07 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ FinalQ4</t>
+          <t>Fed Kugler Speech</t>
         </is>
       </c>
       <c r="C816" t="inlineStr"/>
-      <c r="D816" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E816" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="F816" t="inlineStr">
-        <is>
-          <t>3.0%</t>
-        </is>
-      </c>
+      <c r="D816" t="inlineStr"/>
+      <c r="E816" t="inlineStr"/>
+      <c r="F816" t="inlineStr"/>
       <c r="G816" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>2025-03-06 19:00:00+05:30</t>
+          <t>2025-03-07 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ FinalQ4</t>
+          <t>Baker Hughes Total Rigs CountMAR/07</t>
         </is>
       </c>
       <c r="C817" t="inlineStr"/>
       <c r="D817" t="inlineStr">
         <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="E817" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
-      <c r="F817" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr"/>
+      <c r="F817" t="inlineStr"/>
       <c r="G817" t="n">
         <v>3</v>
       </c>
@@ -23948,59 +23888,55 @@
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>2025-03-06 19:00:00+05:30</t>
+          <t>2025-03-08 01:30:00+05:30</t>
         </is>
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsMAR/01</t>
+          <t>Consumer Credit ChangeJAN</t>
         </is>
       </c>
       <c r="C818" t="inlineStr"/>
       <c r="D818" t="inlineStr">
         <is>
-          <t>242K</t>
+          <t>$40.85B</t>
         </is>
       </c>
       <c r="E818" t="inlineStr">
         <is>
-          <t>235K</t>
+          <t>$14.5B</t>
         </is>
       </c>
       <c r="F818" t="inlineStr">
         <is>
-          <t>250.0K</t>
+          <t>$ -3.0B</t>
         </is>
       </c>
       <c r="G818" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>2025-03-06 20:30:00+05:30</t>
+          <t>2025-03-10 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoMJAN</t>
+          <t>Consumer Inflation ExpectationsFEB</t>
         </is>
       </c>
       <c r="C819" t="inlineStr"/>
       <c r="D819" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="E819" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr"/>
       <c r="F819" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="G819" t="n">
@@ -24010,30 +23946,18 @@
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>2025-03-06 20:30:00+05:30</t>
+          <t>2025-03-10 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoMJAN</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C820" t="inlineStr"/>
-      <c r="D820" t="inlineStr">
-        <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="E820" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
-      <c r="F820" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="D820" t="inlineStr"/>
+      <c r="E820" t="inlineStr"/>
+      <c r="F820" t="inlineStr"/>
       <c r="G820" t="n">
         <v>3</v>
       </c>
@@ -24041,20 +23965,16 @@
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>2025-03-06 21:00:00+05:30</t>
+          <t>2025-03-10 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>EIA Natural Gas Stocks ChangeFEB/28</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C821" t="inlineStr"/>
-      <c r="D821" t="inlineStr">
-        <is>
-          <t>-261Bcf</t>
-        </is>
-      </c>
+      <c r="D821" t="inlineStr"/>
       <c r="E821" t="inlineStr"/>
       <c r="F821" t="inlineStr"/>
       <c r="G821" t="n">
@@ -24064,26 +23984,26 @@
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>2025-03-06 21:00:00+05:30</t>
+          <t>2025-03-11 15:30:00+05:30</t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>EIA Natural Gas Stocks ChangeFEB/28</t>
+          <t>NFIB Business Optimism IndexFEB</t>
         </is>
       </c>
       <c r="C822" t="inlineStr"/>
       <c r="D822" t="inlineStr">
         <is>
-          <t>-261Bcf</t>
-        </is>
-      </c>
-      <c r="E822" t="inlineStr">
-        <is>
-          <t>-96Bcf</t>
-        </is>
-      </c>
-      <c r="F822" t="inlineStr"/>
+          <t>102.8</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr"/>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
       <c r="G822" t="n">
         <v>3</v>
       </c>
@@ -24091,18 +24011,18 @@
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>2025-03-06 22:00:00+05:30</t>
+          <t>2025-03-11 19:25:00+05:30</t>
         </is>
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>Redbook YoYMAR/08</t>
         </is>
       </c>
       <c r="C823" t="inlineStr"/>
       <c r="D823" t="inlineStr">
         <is>
-          <t>4.235%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="E823" t="inlineStr"/>
@@ -24114,22 +24034,26 @@
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>2025-03-06 22:00:00+05:30</t>
+          <t>2025-03-11 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>JOLTs Job QuitsJAN</t>
         </is>
       </c>
       <c r="C824" t="inlineStr"/>
       <c r="D824" t="inlineStr">
         <is>
-          <t>4.235%</t>
+          <t>3.197M</t>
         </is>
       </c>
       <c r="E824" t="inlineStr"/>
-      <c r="F824" t="inlineStr"/>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>3.21M</t>
+        </is>
+      </c>
       <c r="G824" t="n">
         <v>3</v>
       </c>
@@ -24137,43 +24061,43 @@
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>2025-03-06 22:00:00+05:30</t>
+          <t>2025-03-11 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>JOLTs Job OpeningsJAN</t>
         </is>
       </c>
       <c r="C825" t="inlineStr"/>
       <c r="D825" t="inlineStr">
         <is>
-          <t>4.235%</t>
+          <t>7.6M</t>
         </is>
       </c>
       <c r="E825" t="inlineStr"/>
-      <c r="F825" t="inlineStr"/>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>7.5M</t>
+        </is>
+      </c>
       <c r="G825" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>2025-03-06 22:00:00+05:30</t>
+          <t>2025-03-11 21:30:00+05:30</t>
         </is>
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>WASDE Report</t>
         </is>
       </c>
       <c r="C826" t="inlineStr"/>
-      <c r="D826" t="inlineStr">
-        <is>
-          <t>4.235%</t>
-        </is>
-      </c>
+      <c r="D826" t="inlineStr"/>
       <c r="E826" t="inlineStr"/>
       <c r="F826" t="inlineStr"/>
       <c r="G826" t="n">
@@ -24183,18 +24107,18 @@
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>2025-03-06 22:30:00+05:30</t>
+          <t>2025-03-11 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateMAR/06</t>
+          <t>3-Year Note Auction</t>
         </is>
       </c>
       <c r="C827" t="inlineStr"/>
       <c r="D827" t="inlineStr">
         <is>
-          <t>5.94%</t>
+          <t>4.300%</t>
         </is>
       </c>
       <c r="E827" t="inlineStr"/>
@@ -24206,43 +24130,39 @@
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>2025-03-06 22:30:00+05:30</t>
+          <t>2025-03-12 02:00:00+05:30</t>
         </is>
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateMAR/06</t>
+          <t>API Crude Oil Stock ChangeMAR/07</t>
         </is>
       </c>
       <c r="C828" t="inlineStr"/>
       <c r="D828" t="inlineStr">
         <is>
-          <t>5.94%</t>
+          <t>-1.455M</t>
         </is>
       </c>
       <c r="E828" t="inlineStr"/>
       <c r="F828" t="inlineStr"/>
       <c r="G828" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>2025-03-06 22:30:00+05:30</t>
+          <t>2025-03-12 16:30:00+05:30</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateMAR/06</t>
+          <t>MBA Mortgage Market IndexMAR/07</t>
         </is>
       </c>
       <c r="C829" t="inlineStr"/>
-      <c r="D829" t="inlineStr">
-        <is>
-          <t>6.76%</t>
-        </is>
-      </c>
+      <c r="D829" t="inlineStr"/>
       <c r="E829" t="inlineStr"/>
       <c r="F829" t="inlineStr"/>
       <c r="G829" t="n">
@@ -24252,20 +24172,16 @@
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>2025-03-06 22:30:00+05:30</t>
+          <t>2025-03-12 16:30:00+05:30</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateMAR/06</t>
+          <t>MBA Purchase IndexMAR/07</t>
         </is>
       </c>
       <c r="C830" t="inlineStr"/>
-      <c r="D830" t="inlineStr">
-        <is>
-          <t>6.76%</t>
-        </is>
-      </c>
+      <c r="D830" t="inlineStr"/>
       <c r="E830" t="inlineStr"/>
       <c r="F830" t="inlineStr"/>
       <c r="G830" t="n">
@@ -24275,12 +24191,12 @@
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>2025-03-07 02:00:00+05:30</t>
+          <t>2025-03-12 16:30:00+05:30</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
+          <t>MBA Mortgage Refinance IndexMAR/07</t>
         </is>
       </c>
       <c r="C831" t="inlineStr"/>
@@ -24288,22 +24204,26 @@
       <c r="E831" t="inlineStr"/>
       <c r="F831" t="inlineStr"/>
       <c r="G831" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>2025-03-07 02:00:00+05:30</t>
+          <t>2025-03-12 16:30:00+05:30</t>
         </is>
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
+          <t>MBA 30-Year Mortgage RateMAR/07</t>
         </is>
       </c>
       <c r="C832" t="inlineStr"/>
-      <c r="D832" t="inlineStr"/>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>6.73%</t>
+        </is>
+      </c>
       <c r="E832" t="inlineStr"/>
       <c r="F832" t="inlineStr"/>
       <c r="G832" t="n">
@@ -24313,20 +24233,16 @@
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>2025-03-07 03:00:00+05:30</t>
+          <t>2025-03-12 16:30:00+05:30</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>Fed Balance SheetMAR/05</t>
+          <t>MBA Mortgage ApplicationsMAR/07</t>
         </is>
       </c>
       <c r="C833" t="inlineStr"/>
-      <c r="D833" t="inlineStr">
-        <is>
-          <t>$6.77T</t>
-        </is>
-      </c>
+      <c r="D833" t="inlineStr"/>
       <c r="E833" t="inlineStr"/>
       <c r="F833" t="inlineStr"/>
       <c r="G833" t="n">
@@ -24336,37 +24252,53 @@
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>2025-03-07 03:00:00+05:30</t>
+          <t>2025-03-12 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>Fed Balance SheetMAR/05</t>
+          <t>Core Inflation Rate MoMFEB</t>
         </is>
       </c>
       <c r="C834" t="inlineStr"/>
-      <c r="D834" t="inlineStr"/>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E834" t="inlineStr"/>
-      <c r="F834" t="inlineStr"/>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="G834" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>2025-03-07 05:30:00+05:30</t>
+          <t>2025-03-12 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>CPIFEB</t>
         </is>
       </c>
       <c r="C835" t="inlineStr"/>
-      <c r="D835" t="inlineStr"/>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>317.67</t>
+        </is>
+      </c>
       <c r="E835" t="inlineStr"/>
-      <c r="F835" t="inlineStr"/>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>319.6</t>
+        </is>
+      </c>
       <c r="G835" t="n">
         <v>2</v>
       </c>
@@ -24374,18 +24306,26 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>2025-03-07 05:30:00+05:30</t>
+          <t>2025-03-12 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>CPI s.aFEB</t>
         </is>
       </c>
       <c r="C836" t="inlineStr"/>
-      <c r="D836" t="inlineStr"/>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>319.086</t>
+        </is>
+      </c>
       <c r="E836" t="inlineStr"/>
-      <c r="F836" t="inlineStr"/>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>320.4</t>
+        </is>
+      </c>
       <c r="G836" t="n">
         <v>2</v>
       </c>
@@ -24393,55 +24333,51 @@
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>2025-03-07 19:00:00+05:30</t>
+          <t>2025-03-12 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>Government PayrollsFEB</t>
+          <t>Inflation Rate MoMFEB</t>
         </is>
       </c>
       <c r="C837" t="inlineStr"/>
       <c r="D837" t="inlineStr">
         <is>
-          <t>32K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E837" t="inlineStr"/>
       <c r="F837" t="inlineStr">
         <is>
-          <t>-20.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G837" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>2025-03-07 19:00:00+05:30</t>
+          <t>2025-03-12 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsFEB</t>
+          <t>Core Inflation Rate YoYFEB</t>
         </is>
       </c>
       <c r="C838" t="inlineStr"/>
       <c r="D838" t="inlineStr">
         <is>
-          <t>143K</t>
-        </is>
-      </c>
-      <c r="E838" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr"/>
       <c r="F838" t="inlineStr">
         <is>
-          <t>150.0K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G838" t="n">
@@ -24451,43 +24387,43 @@
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>2025-03-07 19:00:00+05:30</t>
+          <t>2025-03-12 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYFEB</t>
+          <t>Inflation Rate YoYFEB</t>
         </is>
       </c>
       <c r="C839" t="inlineStr"/>
       <c r="D839" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E839" t="inlineStr"/>
-      <c r="F839" t="inlineStr"/>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>3.0%</t>
+        </is>
+      </c>
       <c r="G839" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>2025-03-07 19:00:00+05:30</t>
+          <t>2025-03-12 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMFEB</t>
+          <t>EIA Refinery Crude Runs ChangeMAR/07</t>
         </is>
       </c>
       <c r="C840" t="inlineStr"/>
-      <c r="D840" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D840" t="inlineStr"/>
       <c r="E840" t="inlineStr"/>
       <c r="F840" t="inlineStr"/>
       <c r="G840" t="n">
@@ -24497,119 +24433,75 @@
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>2025-03-07 19:00:00+05:30</t>
+          <t>2025-03-12 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsFEB</t>
+          <t>EIA Heating Oil Stocks ChangeMAR/07</t>
         </is>
       </c>
       <c r="C841" t="inlineStr"/>
-      <c r="D841" t="inlineStr">
-        <is>
-          <t>143K</t>
-        </is>
-      </c>
-      <c r="E841" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
-      <c r="F841" t="inlineStr">
-        <is>
-          <t>150.0K</t>
-        </is>
-      </c>
+      <c r="D841" t="inlineStr"/>
+      <c r="E841" t="inlineStr"/>
+      <c r="F841" t="inlineStr"/>
       <c r="G841" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>2025-03-07 19:00:00+05:30</t>
+          <t>2025-03-12 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMFEB</t>
+          <t>EIA Distillate Fuel Production ChangeMAR/07</t>
         </is>
       </c>
       <c r="C842" t="inlineStr"/>
-      <c r="D842" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E842" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="F842" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D842" t="inlineStr"/>
+      <c r="E842" t="inlineStr"/>
+      <c r="F842" t="inlineStr"/>
       <c r="G842" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>2025-03-07 19:00:00+05:30</t>
+          <t>2025-03-12 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>Participation RateFEB</t>
+          <t>EIA Distillate Stocks ChangeMAR/07</t>
         </is>
       </c>
       <c r="C843" t="inlineStr"/>
-      <c r="D843" t="inlineStr">
-        <is>
-          <t>62.6%</t>
-        </is>
-      </c>
+      <c r="D843" t="inlineStr"/>
       <c r="E843" t="inlineStr"/>
-      <c r="F843" t="inlineStr">
-        <is>
-          <t>62.6%</t>
-        </is>
-      </c>
+      <c r="F843" t="inlineStr"/>
       <c r="G843" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>2025-03-07 19:00:00+05:30</t>
+          <t>2025-03-12 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>Average Weekly HoursFEB</t>
+          <t>EIA Crude Oil Imports ChangeMAR/07</t>
         </is>
       </c>
       <c r="C844" t="inlineStr"/>
-      <c r="D844" t="inlineStr">
-        <is>
-          <t>34.1</t>
-        </is>
-      </c>
-      <c r="E844" t="inlineStr">
-        <is>
-          <t>34.2</t>
-        </is>
-      </c>
-      <c r="F844" t="inlineStr">
-        <is>
-          <t>34.1</t>
-        </is>
-      </c>
+      <c r="D844" t="inlineStr"/>
+      <c r="E844" t="inlineStr"/>
+      <c r="F844" t="inlineStr"/>
       <c r="G844" t="n">
         <v>3</v>
       </c>
@@ -24617,26 +24509,18 @@
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>2025-03-07 19:00:00+05:30</t>
+          <t>2025-03-12 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>Government PayrollsFEB</t>
+          <t>EIA Gasoline Production ChangeMAR/07</t>
         </is>
       </c>
       <c r="C845" t="inlineStr"/>
-      <c r="D845" t="inlineStr">
-        <is>
-          <t>32K</t>
-        </is>
-      </c>
+      <c r="D845" t="inlineStr"/>
       <c r="E845" t="inlineStr"/>
-      <c r="F845" t="inlineStr">
-        <is>
-          <t>-20.0K</t>
-        </is>
-      </c>
+      <c r="F845" t="inlineStr"/>
       <c r="G845" t="n">
         <v>3</v>
       </c>
@@ -24644,30 +24528,18 @@
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>2025-03-07 19:00:00+05:30</t>
+          <t>2025-03-12 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsFEB</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeMAR/07</t>
         </is>
       </c>
       <c r="C846" t="inlineStr"/>
-      <c r="D846" t="inlineStr">
-        <is>
-          <t>3K</t>
-        </is>
-      </c>
-      <c r="E846" t="inlineStr">
-        <is>
-          <t>5K</t>
-        </is>
-      </c>
-      <c r="F846" t="inlineStr">
-        <is>
-          <t>6.0K</t>
-        </is>
-      </c>
+      <c r="D846" t="inlineStr"/>
+      <c r="E846" t="inlineStr"/>
+      <c r="F846" t="inlineStr"/>
       <c r="G846" t="n">
         <v>3</v>
       </c>
@@ -24675,330 +24547,250 @@
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>2025-03-07 19:00:00+05:30</t>
+          <t>2025-03-12 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateFEB</t>
+          <t>EIA Gasoline Stocks ChangeMAR/07</t>
         </is>
       </c>
       <c r="C847" t="inlineStr"/>
-      <c r="D847" t="inlineStr">
-        <is>
-          <t>111K</t>
-        </is>
-      </c>
-      <c r="E847" t="inlineStr">
-        <is>
-          <t>143K</t>
-        </is>
-      </c>
-      <c r="F847" t="inlineStr">
-        <is>
-          <t>170.0K</t>
-        </is>
-      </c>
+      <c r="D847" t="inlineStr"/>
+      <c r="E847" t="inlineStr"/>
+      <c r="F847" t="inlineStr"/>
       <c r="G847" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>2025-03-07 19:00:00+05:30</t>
+          <t>2025-03-12 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateFEB</t>
+          <t>EIA Crude Oil Stocks ChangeMAR/07</t>
         </is>
       </c>
       <c r="C848" t="inlineStr"/>
-      <c r="D848" t="inlineStr">
-        <is>
-          <t>7.5%</t>
-        </is>
-      </c>
+      <c r="D848" t="inlineStr"/>
       <c r="E848" t="inlineStr"/>
-      <c r="F848" t="inlineStr">
-        <is>
-          <t>7.6%</t>
-        </is>
-      </c>
+      <c r="F848" t="inlineStr"/>
       <c r="G848" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>2025-03-07 19:00:00+05:30</t>
+          <t>2025-03-12 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYFEB</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C849" t="inlineStr"/>
-      <c r="D849" t="inlineStr">
-        <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="E849" t="inlineStr">
-        <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="F849" t="inlineStr">
-        <is>
-          <t>4.1%</t>
-        </is>
-      </c>
+      <c r="D849" t="inlineStr"/>
+      <c r="E849" t="inlineStr"/>
+      <c r="F849" t="inlineStr"/>
       <c r="G849" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>2025-03-07 19:00:00+05:30</t>
+          <t>2025-03-12 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>Unemployment RateFEB</t>
+          <t>10-Year Note Auction</t>
         </is>
       </c>
       <c r="C850" t="inlineStr"/>
       <c r="D850" t="inlineStr">
         <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="E850" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="F850" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+          <t>4.632%</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr"/>
+      <c r="F850" t="inlineStr"/>
       <c r="G850" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>2025-03-07 19:00:00+05:30</t>
+          <t>2025-03-12 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateFEB</t>
+          <t>Monthly Budget StatementFEB</t>
         </is>
       </c>
       <c r="C851" t="inlineStr"/>
       <c r="D851" t="inlineStr">
         <is>
-          <t>111K</t>
-        </is>
-      </c>
-      <c r="E851" t="inlineStr">
-        <is>
-          <t>143K</t>
-        </is>
-      </c>
+          <t>$-129B</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr"/>
       <c r="F851" t="inlineStr">
         <is>
-          <t>170.0K</t>
+          <t>$-90.0B</t>
         </is>
       </c>
       <c r="G851" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>2025-03-07 19:00:00+05:30</t>
+          <t>2025-03-13 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>Unemployment RateFEB</t>
+          <t>PPI YoYFEB</t>
         </is>
       </c>
       <c r="C852" t="inlineStr"/>
       <c r="D852" t="inlineStr">
         <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="E852" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr"/>
       <c r="F852" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G852" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>2025-03-07 19:00:00+05:30</t>
+          <t>2025-03-13 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMFEB</t>
+          <t>PPI Ex Food, Energy and Trade YoYFEB</t>
         </is>
       </c>
       <c r="C853" t="inlineStr"/>
       <c r="D853" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E853" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.4%</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr"/>
       <c r="F853" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G853" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>2025-03-07 19:00:00+05:30</t>
+          <t>2025-03-13 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYFEB</t>
+          <t>Continuing Jobless ClaimsMAR/01</t>
         </is>
       </c>
       <c r="C854" t="inlineStr"/>
-      <c r="D854" t="inlineStr">
-        <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="E854" t="inlineStr">
-        <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="F854" t="inlineStr">
-        <is>
-          <t>4.1%</t>
-        </is>
-      </c>
+      <c r="D854" t="inlineStr"/>
+      <c r="E854" t="inlineStr"/>
+      <c r="F854" t="inlineStr"/>
       <c r="G854" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>2025-03-07 19:00:00+05:30</t>
+          <t>2025-03-13 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>Participation RateFEB</t>
+          <t>Jobless Claims 4-week AverageMAR/08</t>
         </is>
       </c>
       <c r="C855" t="inlineStr"/>
-      <c r="D855" t="inlineStr">
-        <is>
-          <t>62.6%</t>
-        </is>
-      </c>
+      <c r="D855" t="inlineStr"/>
       <c r="E855" t="inlineStr"/>
-      <c r="F855" t="inlineStr">
-        <is>
-          <t>62.6%</t>
-        </is>
-      </c>
+      <c r="F855" t="inlineStr"/>
       <c r="G855" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>2025-03-07 19:00:00+05:30</t>
+          <t>2025-03-13 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>Average Weekly HoursFEB</t>
+          <t>PPI MoMFEB</t>
         </is>
       </c>
       <c r="C856" t="inlineStr"/>
       <c r="D856" t="inlineStr">
         <is>
-          <t>34.1</t>
-        </is>
-      </c>
-      <c r="E856" t="inlineStr">
-        <is>
-          <t>34.2</t>
-        </is>
-      </c>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr"/>
       <c r="F856" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G856" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>2025-03-07 19:00:00+05:30</t>
+          <t>2025-03-13 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsFEB</t>
+          <t>PPIFEB</t>
         </is>
       </c>
       <c r="C857" t="inlineStr"/>
       <c r="D857" t="inlineStr">
         <is>
-          <t>3K</t>
-        </is>
-      </c>
-      <c r="E857" t="inlineStr">
-        <is>
-          <t>5K</t>
-        </is>
-      </c>
+          <t>147.716</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr"/>
       <c r="F857" t="inlineStr">
         <is>
-          <t>6.0K</t>
+          <t>148.2</t>
         </is>
       </c>
       <c r="G857" t="n">
@@ -25008,24 +24800,24 @@
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>2025-03-07 19:00:00+05:30</t>
+          <t>2025-03-13 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateFEB</t>
+          <t>Core PPI YoYFEB</t>
         </is>
       </c>
       <c r="C858" t="inlineStr"/>
       <c r="D858" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="E858" t="inlineStr"/>
       <c r="F858" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G858" t="n">
@@ -25035,31 +24827,39 @@
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>2025-03-07 20:45:00+05:30</t>
+          <t>2025-03-13 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
+          <t>PPI Ex Food, Energy and Trade MoMFEB</t>
         </is>
       </c>
       <c r="C859" t="inlineStr"/>
-      <c r="D859" t="inlineStr"/>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E859" t="inlineStr"/>
-      <c r="F859" t="inlineStr"/>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="G859" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>2025-03-07 20:45:00+05:30</t>
+          <t>2025-03-13 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
+          <t>Initial Jobless ClaimsMAR/08</t>
         </is>
       </c>
       <c r="C860" t="inlineStr"/>
@@ -25073,18 +24873,26 @@
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>2025-03-07 21:15:00+05:30</t>
+          <t>2025-03-13 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>Fed Williams Speech</t>
+          <t>Core PPI MoMFEB</t>
         </is>
       </c>
       <c r="C861" t="inlineStr"/>
-      <c r="D861" t="inlineStr"/>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E861" t="inlineStr"/>
-      <c r="F861" t="inlineStr"/>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="G861" t="n">
         <v>2</v>
       </c>
@@ -25092,12 +24900,12 @@
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>2025-03-07 21:15:00+05:30</t>
+          <t>2025-03-13 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>Fed Williams Speech</t>
+          <t>EIA Natural Gas Stocks ChangeMAR/07</t>
         </is>
       </c>
       <c r="C862" t="inlineStr"/>
@@ -25105,18 +24913,18 @@
       <c r="E862" t="inlineStr"/>
       <c r="F862" t="inlineStr"/>
       <c r="G862" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>2025-03-07 22:50:00+05:30</t>
+          <t>2025-03-13 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C863" t="inlineStr"/>
@@ -25124,18 +24932,18 @@
       <c r="E863" t="inlineStr"/>
       <c r="F863" t="inlineStr"/>
       <c r="G863" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>2025-03-07 22:50:00+05:30</t>
+          <t>2025-03-13 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C864" t="inlineStr"/>
@@ -25143,18 +24951,18 @@
       <c r="E864" t="inlineStr"/>
       <c r="F864" t="inlineStr"/>
       <c r="G864" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>2025-03-07 23:00:00+05:30</t>
+          <t>2025-03-13 21:30:00+05:30</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>Fed Chair Powell Speech</t>
+          <t>30-Year Mortgage RateMAR/13</t>
         </is>
       </c>
       <c r="C865" t="inlineStr"/>
@@ -25162,18 +24970,18 @@
       <c r="E865" t="inlineStr"/>
       <c r="F865" t="inlineStr"/>
       <c r="G865" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>2025-03-07 23:00:00+05:30</t>
+          <t>2025-03-13 21:30:00+05:30</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>Fed Chair Powell Speech</t>
+          <t>15-Year Mortgage RateMAR/13</t>
         </is>
       </c>
       <c r="C866" t="inlineStr"/>
@@ -25181,45 +24989,45 @@
       <c r="E866" t="inlineStr"/>
       <c r="F866" t="inlineStr"/>
       <c r="G866" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>2025-03-07 23:30:00+05:30</t>
+          <t>2025-03-13 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>30-Year Bond Auction</t>
         </is>
       </c>
       <c r="C867" t="inlineStr"/>
-      <c r="D867" t="inlineStr"/>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>4.748%</t>
+        </is>
+      </c>
       <c r="E867" t="inlineStr"/>
       <c r="F867" t="inlineStr"/>
       <c r="G867" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>2025-03-07 23:30:00+05:30</t>
+          <t>2025-03-14 02:00:00+05:30</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYFEB</t>
+          <t>Fed Balance SheetMAR/12</t>
         </is>
       </c>
       <c r="C868" t="inlineStr"/>
-      <c r="D868" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
+      <c r="D868" t="inlineStr"/>
       <c r="E868" t="inlineStr"/>
       <c r="F868" t="inlineStr"/>
       <c r="G868" t="n">
@@ -25229,22 +25037,26 @@
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>2025-03-07 23:30:00+05:30</t>
+          <t>2025-03-14 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountMAR/07</t>
+          <t>Michigan Current Conditions PrelMAR</t>
         </is>
       </c>
       <c r="C869" t="inlineStr"/>
       <c r="D869" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="E869" t="inlineStr"/>
-      <c r="F869" t="inlineStr"/>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>68.4</t>
+        </is>
+      </c>
       <c r="G869" t="n">
         <v>3</v>
       </c>
@@ -25252,22 +25064,26 @@
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>2025-03-07 23:30:00+05:30</t>
+          <t>2025-03-14 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMFEB</t>
+          <t>Michigan Inflation Expectations PrelMAR</t>
         </is>
       </c>
       <c r="C870" t="inlineStr"/>
       <c r="D870" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E870" t="inlineStr"/>
-      <c r="F870" t="inlineStr"/>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>4.4%</t>
+        </is>
+      </c>
       <c r="G870" t="n">
         <v>3</v>
       </c>
@@ -25275,22 +25091,26 @@
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>2025-03-07 23:30:00+05:30</t>
+          <t>2025-03-14 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYFEB</t>
+          <t>Michigan 5 Year Inflation Expectations PrelMAR</t>
         </is>
       </c>
       <c r="C871" t="inlineStr"/>
       <c r="D871" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="E871" t="inlineStr"/>
-      <c r="F871" t="inlineStr"/>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>3.4%</t>
+        </is>
+      </c>
       <c r="G871" t="n">
         <v>3</v>
       </c>
@@ -25298,45 +25118,45 @@
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>2025-03-07 23:30:00+05:30</t>
+          <t>2025-03-14 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMFEB</t>
+          <t>Michigan Consumer Sentiment PrelMAR</t>
         </is>
       </c>
       <c r="C872" t="inlineStr"/>
-      <c r="D872" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D872" t="inlineStr"/>
       <c r="E872" t="inlineStr"/>
-      <c r="F872" t="inlineStr"/>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>67.2</t>
+        </is>
+      </c>
       <c r="G872" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>2025-03-07 23:30:00+05:30</t>
+          <t>2025-03-14 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountMAR/07</t>
+          <t>Michigan Consumer Expectations PrelMAR</t>
         </is>
       </c>
       <c r="C873" t="inlineStr"/>
-      <c r="D873" t="inlineStr">
-        <is>
-          <t>593</t>
-        </is>
-      </c>
+      <c r="D873" t="inlineStr"/>
       <c r="E873" t="inlineStr"/>
-      <c r="F873" t="inlineStr"/>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
       <c r="G873" t="n">
         <v>3</v>
       </c>
@@ -25344,20 +25164,16 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>2025-03-07 23:30:00+05:30</t>
+          <t>2025-03-14 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountMAR/07</t>
+          <t>Baker Hughes Total Rigs CountMAR/14</t>
         </is>
       </c>
       <c r="C874" t="inlineStr"/>
-      <c r="D874" t="inlineStr">
-        <is>
-          <t>489</t>
-        </is>
-      </c>
+      <c r="D874" t="inlineStr"/>
       <c r="E874" t="inlineStr"/>
       <c r="F874" t="inlineStr"/>
       <c r="G874" t="n">
@@ -25367,12 +25183,12 @@
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>2025-03-07 23:30:00+05:30</t>
+          <t>2025-03-14 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>Baker Hughes Oil Rig CountMAR/14</t>
         </is>
       </c>
       <c r="C875" t="inlineStr"/>
@@ -25380,142 +25196,134 @@
       <c r="E875" t="inlineStr"/>
       <c r="F875" t="inlineStr"/>
       <c r="G875" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>2025-03-07 23:30:00+05:30</t>
+          <t>2025-03-17 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountMAR/07</t>
+          <t>Retail Sales MoMFEB</t>
         </is>
       </c>
       <c r="C876" t="inlineStr"/>
       <c r="D876" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="E876" t="inlineStr"/>
-      <c r="F876" t="inlineStr"/>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="G876" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>2025-03-08 01:30:00+05:30</t>
+          <t>2025-03-17 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>Consumer Credit ChangeJAN</t>
+          <t>NY Empire State Manufacturing IndexMAR</t>
         </is>
       </c>
       <c r="C877" t="inlineStr"/>
       <c r="D877" t="inlineStr">
         <is>
-          <t>$40.85B</t>
-        </is>
-      </c>
-      <c r="E877" t="inlineStr">
-        <is>
-          <t>$14.5B</t>
-        </is>
-      </c>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr"/>
       <c r="F877" t="inlineStr">
         <is>
-          <t>$ -3.0B</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G877" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>2025-03-08 01:30:00+05:30</t>
+          <t>2025-03-17 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>Consumer Credit ChangeJAN</t>
+          <t>Retail Sales Control Group MoMFEB</t>
         </is>
       </c>
       <c r="C878" t="inlineStr"/>
       <c r="D878" t="inlineStr">
         <is>
-          <t>$40.85B</t>
-        </is>
-      </c>
-      <c r="E878" t="inlineStr">
-        <is>
-          <t>$14.5B</t>
-        </is>
-      </c>
-      <c r="F878" t="inlineStr">
-        <is>
-          <t>$ -3.0B</t>
-        </is>
-      </c>
+          <t>-0.8%</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr"/>
+      <c r="F878" t="inlineStr"/>
       <c r="G878" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>2025-03-10 20:30:00+05:30</t>
+          <t>2025-03-17 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>Consumer Inflation ExpectationsFEB</t>
+          <t>Retail Sales Ex Autos MoMFEB</t>
         </is>
       </c>
       <c r="C879" t="inlineStr"/>
       <c r="D879" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="E879" t="inlineStr"/>
       <c r="F879" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G879" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>2025-03-10 20:30:00+05:30</t>
+          <t>2025-03-17 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>Consumer Inflation ExpectationsFEB</t>
+          <t>Retail Sales Ex Gas/Autos MoMFEB</t>
         </is>
       </c>
       <c r="C880" t="inlineStr"/>
       <c r="D880" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E880" t="inlineStr"/>
       <c r="F880" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G880" t="n">
@@ -25525,18 +25333,26 @@
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>2025-03-10 22:00:00+05:30</t>
+          <t>2025-03-17 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>Retail Sales YoYFEB</t>
         </is>
       </c>
       <c r="C881" t="inlineStr"/>
-      <c r="D881" t="inlineStr"/>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="E881" t="inlineStr"/>
-      <c r="F881" t="inlineStr"/>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>3.5%</t>
+        </is>
+      </c>
       <c r="G881" t="n">
         <v>3</v>
       </c>
@@ -25544,18 +25360,22 @@
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>2025-03-10 22:00:00+05:30</t>
+          <t>2025-03-17 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>Retail Inventories Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C882" t="inlineStr"/>
       <c r="D882" t="inlineStr"/>
       <c r="E882" t="inlineStr"/>
-      <c r="F882" t="inlineStr"/>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="G882" t="n">
         <v>3</v>
       </c>
@@ -25563,64 +25383,72 @@
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>2025-03-10 22:00:00+05:30</t>
+          <t>2025-03-17 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>NAHB Housing Market IndexMAR</t>
         </is>
       </c>
       <c r="C883" t="inlineStr"/>
-      <c r="D883" t="inlineStr"/>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
       <c r="E883" t="inlineStr"/>
-      <c r="F883" t="inlineStr"/>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="G883" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>2025-03-10 22:00:00+05:30</t>
+          <t>2025-03-17 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>Business Inventories MoMJAN</t>
         </is>
       </c>
       <c r="C884" t="inlineStr"/>
-      <c r="D884" t="inlineStr"/>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
       <c r="E884" t="inlineStr"/>
-      <c r="F884" t="inlineStr"/>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="G884" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>2025-03-11 15:30:00+05:30</t>
+          <t>2025-03-17 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>NFIB Business Optimism IndexFEB</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C885" t="inlineStr"/>
-      <c r="D885" t="inlineStr">
-        <is>
-          <t>102.8</t>
-        </is>
-      </c>
+      <c r="D885" t="inlineStr"/>
       <c r="E885" t="inlineStr"/>
-      <c r="F885" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
+      <c r="F885" t="inlineStr"/>
       <c r="G885" t="n">
         <v>3</v>
       </c>
@@ -25628,26 +25456,18 @@
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>2025-03-11 15:30:00+05:30</t>
+          <t>2025-03-17 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>NFIB Business Optimism IndexFEB</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C886" t="inlineStr"/>
-      <c r="D886" t="inlineStr">
-        <is>
-          <t>102.8</t>
-        </is>
-      </c>
+      <c r="D886" t="inlineStr"/>
       <c r="E886" t="inlineStr"/>
-      <c r="F886" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
+      <c r="F886" t="inlineStr"/>
       <c r="G886" t="n">
         <v>3</v>
       </c>
@@ -25655,20 +25475,16 @@
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>2025-03-11 19:25:00+05:30</t>
+          <t>2025-03-17 21:30:00+05:30</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>Redbook YoYMAR/08</t>
+          <t>NOPA Crush Report</t>
         </is>
       </c>
       <c r="C887" t="inlineStr"/>
-      <c r="D887" t="inlineStr">
-        <is>
-          <t>6.6%</t>
-        </is>
-      </c>
+      <c r="D887" t="inlineStr"/>
       <c r="E887" t="inlineStr"/>
       <c r="F887" t="inlineStr"/>
       <c r="G887" t="n">
@@ -25678,22 +25494,26 @@
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>2025-03-11 19:25:00+05:30</t>
+          <t>2025-03-18 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>Redbook YoYMAR/08</t>
+          <t>Export Prices YoYFEB</t>
         </is>
       </c>
       <c r="C888" t="inlineStr"/>
       <c r="D888" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="E888" t="inlineStr"/>
-      <c r="F888" t="inlineStr"/>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>3.0%</t>
+        </is>
+      </c>
       <c r="G888" t="n">
         <v>3</v>
       </c>
@@ -25701,24 +25521,24 @@
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>2025-03-11 19:30:00+05:30</t>
+          <t>2025-03-18 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsJAN</t>
+          <t>Import Prices YoYFEB</t>
         </is>
       </c>
       <c r="C889" t="inlineStr"/>
       <c r="D889" t="inlineStr">
         <is>
-          <t>3.197M</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E889" t="inlineStr"/>
       <c r="F889" t="inlineStr">
         <is>
-          <t>3.21M</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="G889" t="n">
@@ -25728,162 +25548,170 @@
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>2025-03-11 19:30:00+05:30</t>
+          <t>2025-03-18 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsJAN</t>
+          <t>Housing Starts MoMFEB</t>
         </is>
       </c>
       <c r="C890" t="inlineStr"/>
       <c r="D890" t="inlineStr">
         <is>
-          <t>7.6M</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="E890" t="inlineStr"/>
       <c r="F890" t="inlineStr">
         <is>
-          <t>7.5M</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="G890" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>2025-03-11 19:30:00+05:30</t>
+          <t>2025-03-18 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsJAN</t>
+          <t>Export Prices MoMFEB</t>
         </is>
       </c>
       <c r="C891" t="inlineStr"/>
       <c r="D891" t="inlineStr">
         <is>
-          <t>3.197M</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="E891" t="inlineStr"/>
       <c r="F891" t="inlineStr">
         <is>
-          <t>3.21M</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="G891" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>2025-03-11 19:30:00+05:30</t>
+          <t>2025-03-18 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsJAN</t>
+          <t>Import Prices MoMFEB</t>
         </is>
       </c>
       <c r="C892" t="inlineStr"/>
       <c r="D892" t="inlineStr">
         <is>
-          <t>7.6M</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E892" t="inlineStr"/>
       <c r="F892" t="inlineStr">
         <is>
-          <t>7.5M</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G892" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>2025-03-11 21:30:00+05:30</t>
+          <t>2025-03-18 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
+          <t>Housing StartsFEB</t>
         </is>
       </c>
       <c r="C893" t="inlineStr"/>
-      <c r="D893" t="inlineStr"/>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>1.366M</t>
+        </is>
+      </c>
       <c r="E893" t="inlineStr"/>
-      <c r="F893" t="inlineStr"/>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>1.34M</t>
+        </is>
+      </c>
       <c r="G893" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>2025-03-11 21:30:00+05:30</t>
+          <t>2025-03-18 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
+          <t>Building Permits PrelFEB</t>
         </is>
       </c>
       <c r="C894" t="inlineStr"/>
-      <c r="D894" t="inlineStr"/>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>1.473M</t>
+        </is>
+      </c>
       <c r="E894" t="inlineStr"/>
       <c r="F894" t="inlineStr"/>
       <c r="G894" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>2025-03-11 22:30:00+05:30</t>
+          <t>2025-03-18 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>3-Year Note Auction</t>
+          <t>Building Permits MoM PrelFEB</t>
         </is>
       </c>
       <c r="C895" t="inlineStr"/>
       <c r="D895" t="inlineStr">
         <is>
-          <t>4.300%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="E895" t="inlineStr"/>
       <c r="F895" t="inlineStr"/>
       <c r="G895" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>2025-03-11 22:30:00+05:30</t>
+          <t>2025-03-18 18:25:00+05:30</t>
         </is>
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>3-Year Note Auction</t>
+          <t>Redbook YoYMAR/15</t>
         </is>
       </c>
       <c r="C896" t="inlineStr"/>
-      <c r="D896" t="inlineStr">
-        <is>
-          <t>4.300%</t>
-        </is>
-      </c>
+      <c r="D896" t="inlineStr"/>
       <c r="E896" t="inlineStr"/>
       <c r="F896" t="inlineStr"/>
       <c r="G896" t="n">
@@ -25893,22 +25721,26 @@
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>2025-03-12 02:00:00+05:30</t>
+          <t>2025-03-18 18:45:00+05:30</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>API Crude Oil Stock ChangeMAR/07</t>
+          <t>Industrial Production MoMFEB</t>
         </is>
       </c>
       <c r="C897" t="inlineStr"/>
       <c r="D897" t="inlineStr">
         <is>
-          <t>-1.455M</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E897" t="inlineStr"/>
-      <c r="F897" t="inlineStr"/>
+      <c r="F897" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="G897" t="n">
         <v>2</v>
       </c>
@@ -25916,41 +25748,53 @@
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>2025-03-12 02:00:00+05:30</t>
+          <t>2025-03-18 18:45:00+05:30</t>
         </is>
       </c>
       <c r="B898" t="inlineStr">
         <is>
-          <t>API Crude Oil Stock ChangeMAR/07</t>
+          <t>Capacity UtilizationFEB</t>
         </is>
       </c>
       <c r="C898" t="inlineStr"/>
       <c r="D898" t="inlineStr">
         <is>
-          <t>-1.455M</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="E898" t="inlineStr"/>
-      <c r="F898" t="inlineStr"/>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="G898" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>2025-03-12 16:30:00+05:30</t>
+          <t>2025-03-18 18:45:00+05:30</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexMAR/07</t>
+          <t>Industrial Production YoYFEB</t>
         </is>
       </c>
       <c r="C899" t="inlineStr"/>
-      <c r="D899" t="inlineStr"/>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
       <c r="E899" t="inlineStr"/>
-      <c r="F899" t="inlineStr"/>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="G899" t="n">
         <v>3</v>
       </c>
@@ -25958,18 +25802,26 @@
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>2025-03-12 16:30:00+05:30</t>
+          <t>2025-03-18 18:45:00+05:30</t>
         </is>
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexMAR/07</t>
+          <t>Manufacturing Production MoMFEB</t>
         </is>
       </c>
       <c r="C900" t="inlineStr"/>
-      <c r="D900" t="inlineStr"/>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="E900" t="inlineStr"/>
-      <c r="F900" t="inlineStr"/>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="G900" t="n">
         <v>3</v>
       </c>
@@ -25977,18 +25829,26 @@
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>2025-03-12 16:30:00+05:30</t>
+          <t>2025-03-18 18:45:00+05:30</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexMAR/07</t>
+          <t>Manufacturing Production YoYFEB</t>
         </is>
       </c>
       <c r="C901" t="inlineStr"/>
-      <c r="D901" t="inlineStr"/>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
       <c r="E901" t="inlineStr"/>
-      <c r="F901" t="inlineStr"/>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>1.3%</t>
+        </is>
+      </c>
       <c r="G901" t="n">
         <v>3</v>
       </c>
@@ -25996,16 +25856,20 @@
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>2025-03-12 16:30:00+05:30</t>
+          <t>2025-03-18 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexMAR/07</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C902" t="inlineStr"/>
-      <c r="D902" t="inlineStr"/>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>4.05%</t>
+        </is>
+      </c>
       <c r="E902" t="inlineStr"/>
       <c r="F902" t="inlineStr"/>
       <c r="G902" t="n">
@@ -26015,16 +25879,20 @@
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>2025-03-12 16:30:00+05:30</t>
+          <t>2025-03-18 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexMAR/07</t>
+          <t>20-Year Bond Auction</t>
         </is>
       </c>
       <c r="C903" t="inlineStr"/>
-      <c r="D903" t="inlineStr"/>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>4.83%</t>
+        </is>
+      </c>
       <c r="E903" t="inlineStr"/>
       <c r="F903" t="inlineStr"/>
       <c r="G903" t="n">
@@ -26034,35 +25902,31 @@
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>2025-03-12 16:30:00+05:30</t>
+          <t>2025-03-19 02:00:00+05:30</t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsMAR/07</t>
+          <t>API Crude Oil Stock ChangeMAR/14</t>
         </is>
       </c>
       <c r="C904" t="inlineStr"/>
-      <c r="D904" t="inlineStr">
-        <is>
-          <t>20.4%</t>
-        </is>
-      </c>
+      <c r="D904" t="inlineStr"/>
       <c r="E904" t="inlineStr"/>
       <c r="F904" t="inlineStr"/>
       <c r="G904" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t>2025-03-12 16:30:00+05:30</t>
+          <t>2025-03-19 16:30:00+05:30</t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexMAR/07</t>
+          <t>MBA 30-Year Mortgage RateMAR/14</t>
         </is>
       </c>
       <c r="C905" t="inlineStr"/>
@@ -26070,64 +25934,56 @@
       <c r="E905" t="inlineStr"/>
       <c r="F905" t="inlineStr"/>
       <c r="G905" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>2025-03-12 16:30:00+05:30</t>
+          <t>2025-03-19 16:30:00+05:30</t>
         </is>
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateMAR/07</t>
+          <t>MBA Mortgage ApplicationsMAR/14</t>
         </is>
       </c>
       <c r="C906" t="inlineStr"/>
-      <c r="D906" t="inlineStr">
-        <is>
-          <t>6.73%</t>
-        </is>
-      </c>
+      <c r="D906" t="inlineStr"/>
       <c r="E906" t="inlineStr"/>
       <c r="F906" t="inlineStr"/>
       <c r="G906" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>2025-03-12 16:30:00+05:30</t>
+          <t>2025-03-19 16:30:00+05:30</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateMAR/07</t>
+          <t>MBA Mortgage Market IndexMAR/14</t>
         </is>
       </c>
       <c r="C907" t="inlineStr"/>
-      <c r="D907" t="inlineStr">
-        <is>
-          <t>6.73%</t>
-        </is>
-      </c>
+      <c r="D907" t="inlineStr"/>
       <c r="E907" t="inlineStr"/>
       <c r="F907" t="inlineStr"/>
       <c r="G907" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>2025-03-12 16:30:00+05:30</t>
+          <t>2025-03-19 16:30:00+05:30</t>
         </is>
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsMAR/07</t>
+          <t>MBA Mortgage Refinance IndexMAR/14</t>
         </is>
       </c>
       <c r="C908" t="inlineStr"/>
@@ -26141,215 +25997,151 @@
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>2025-03-12 18:00:00+05:30</t>
+          <t>2025-03-19 16:30:00+05:30</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYFEB</t>
+          <t>MBA Purchase IndexMAR/14</t>
         </is>
       </c>
       <c r="C909" t="inlineStr"/>
-      <c r="D909" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
+      <c r="D909" t="inlineStr"/>
       <c r="E909" t="inlineStr"/>
-      <c r="F909" t="inlineStr">
-        <is>
-          <t>3.0%</t>
-        </is>
-      </c>
+      <c r="F909" t="inlineStr"/>
       <c r="G909" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>2025-03-12 18:00:00+05:30</t>
+          <t>2025-03-19 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B910" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMFEB</t>
+          <t>EIA Heating Oil Stocks ChangeMAR/14</t>
         </is>
       </c>
       <c r="C910" t="inlineStr"/>
-      <c r="D910" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D910" t="inlineStr"/>
       <c r="E910" t="inlineStr"/>
-      <c r="F910" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="F910" t="inlineStr"/>
       <c r="G910" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>2025-03-12 18:00:00+05:30</t>
+          <t>2025-03-19 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMFEB</t>
+          <t>EIA Gasoline Production ChangeMAR/14</t>
         </is>
       </c>
       <c r="C911" t="inlineStr"/>
-      <c r="D911" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D911" t="inlineStr"/>
       <c r="E911" t="inlineStr"/>
-      <c r="F911" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="F911" t="inlineStr"/>
       <c r="G911" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>2025-03-12 18:00:00+05:30</t>
+          <t>2025-03-19 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t>CPIFEB</t>
+          <t>EIA Distillate Stocks ChangeMAR/14</t>
         </is>
       </c>
       <c r="C912" t="inlineStr"/>
-      <c r="D912" t="inlineStr">
-        <is>
-          <t>317.67</t>
-        </is>
-      </c>
+      <c r="D912" t="inlineStr"/>
       <c r="E912" t="inlineStr"/>
-      <c r="F912" t="inlineStr">
-        <is>
-          <t>319.6</t>
-        </is>
-      </c>
+      <c r="F912" t="inlineStr"/>
       <c r="G912" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>2025-03-12 18:00:00+05:30</t>
+          <t>2025-03-19 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYFEB</t>
+          <t>EIA Refinery Crude Runs ChangeMAR/14</t>
         </is>
       </c>
       <c r="C913" t="inlineStr"/>
-      <c r="D913" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D913" t="inlineStr"/>
       <c r="E913" t="inlineStr"/>
-      <c r="F913" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="F913" t="inlineStr"/>
       <c r="G913" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t>2025-03-12 18:00:00+05:30</t>
+          <t>2025-03-19 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B914" t="inlineStr">
         <is>
-          <t>CPIFEB</t>
+          <t>EIA Distillate Fuel Production ChangeMAR/14</t>
         </is>
       </c>
       <c r="C914" t="inlineStr"/>
-      <c r="D914" t="inlineStr">
-        <is>
-          <t>317.67</t>
-        </is>
-      </c>
+      <c r="D914" t="inlineStr"/>
       <c r="E914" t="inlineStr"/>
-      <c r="F914" t="inlineStr">
-        <is>
-          <t>319.6</t>
-        </is>
-      </c>
+      <c r="F914" t="inlineStr"/>
       <c r="G914" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>2025-03-12 18:00:00+05:30</t>
+          <t>2025-03-19 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMFEB</t>
+          <t>EIA Crude Oil Imports ChangeMAR/14</t>
         </is>
       </c>
       <c r="C915" t="inlineStr"/>
-      <c r="D915" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+      <c r="D915" t="inlineStr"/>
       <c r="E915" t="inlineStr"/>
-      <c r="F915" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="F915" t="inlineStr"/>
       <c r="G915" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>2025-03-12 18:00:00+05:30</t>
+          <t>2025-03-19 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>CPI s.aFEB</t>
+          <t>EIA Gasoline Stocks ChangeMAR/14</t>
         </is>
       </c>
       <c r="C916" t="inlineStr"/>
-      <c r="D916" t="inlineStr">
-        <is>
-          <t>319.086</t>
-        </is>
-      </c>
+      <c r="D916" t="inlineStr"/>
       <c r="E916" t="inlineStr"/>
-      <c r="F916" t="inlineStr">
-        <is>
-          <t>320.4</t>
-        </is>
-      </c>
+      <c r="F916" t="inlineStr"/>
       <c r="G916" t="n">
         <v>2</v>
       </c>
@@ -26357,120 +26149,96 @@
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>2025-03-12 18:00:00+05:30</t>
+          <t>2025-03-19 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>CPI s.aFEB</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeMAR/14</t>
         </is>
       </c>
       <c r="C917" t="inlineStr"/>
-      <c r="D917" t="inlineStr">
-        <is>
-          <t>319.086</t>
-        </is>
-      </c>
+      <c r="D917" t="inlineStr"/>
       <c r="E917" t="inlineStr"/>
-      <c r="F917" t="inlineStr">
-        <is>
-          <t>320.4</t>
-        </is>
-      </c>
+      <c r="F917" t="inlineStr"/>
       <c r="G917" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>2025-03-12 18:00:00+05:30</t>
+          <t>2025-03-19 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMFEB</t>
+          <t>EIA Crude Oil Stocks ChangeMAR/14</t>
         </is>
       </c>
       <c r="C918" t="inlineStr"/>
-      <c r="D918" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+      <c r="D918" t="inlineStr"/>
       <c r="E918" t="inlineStr"/>
-      <c r="F918" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="F918" t="inlineStr"/>
       <c r="G918" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>2025-03-12 18:00:00+05:30</t>
+          <t>2025-03-19 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYFEB</t>
+          <t>Interest Rate Projection - Current</t>
         </is>
       </c>
       <c r="C919" t="inlineStr"/>
       <c r="D919" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="E919" t="inlineStr"/>
-      <c r="F919" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="F919" t="inlineStr"/>
       <c r="G919" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>2025-03-12 18:00:00+05:30</t>
+          <t>2025-03-19 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYFEB</t>
+          <t>Interest Rate Projection - 2nd Yr</t>
         </is>
       </c>
       <c r="C920" t="inlineStr"/>
       <c r="D920" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E920" t="inlineStr"/>
-      <c r="F920" t="inlineStr">
-        <is>
-          <t>3.0%</t>
-        </is>
-      </c>
+      <c r="F920" t="inlineStr"/>
       <c r="G920" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>2025-03-12 20:00:00+05:30</t>
+          <t>2025-03-19 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeMAR/07</t>
+          <t>International Monetary Market (IMM) Date</t>
         </is>
       </c>
       <c r="C921" t="inlineStr"/>
@@ -26484,12 +26252,12 @@
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>2025-03-12 20:00:00+05:30</t>
+          <t>2025-03-19 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeMAR/07</t>
+          <t>FOMC Economic Projections</t>
         </is>
       </c>
       <c r="C922" t="inlineStr"/>
@@ -26497,41 +26265,53 @@
       <c r="E922" t="inlineStr"/>
       <c r="F922" t="inlineStr"/>
       <c r="G922" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>2025-03-12 20:00:00+05:30</t>
+          <t>2025-03-19 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeMAR/07</t>
+          <t>Fed Interest Rate Decision</t>
         </is>
       </c>
       <c r="C923" t="inlineStr"/>
-      <c r="D923" t="inlineStr"/>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>4.5%</t>
+        </is>
+      </c>
       <c r="E923" t="inlineStr"/>
-      <c r="F923" t="inlineStr"/>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>4.5%</t>
+        </is>
+      </c>
       <c r="G923" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>2025-03-12 20:00:00+05:30</t>
+          <t>2025-03-19 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeMAR/07</t>
+          <t>Interest Rate Projection - 1st Yr</t>
         </is>
       </c>
       <c r="C924" t="inlineStr"/>
-      <c r="D924" t="inlineStr"/>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>3.9%</t>
+        </is>
+      </c>
       <c r="E924" t="inlineStr"/>
       <c r="F924" t="inlineStr"/>
       <c r="G924" t="n">
@@ -26541,16 +26321,20 @@
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>2025-03-12 20:00:00+05:30</t>
+          <t>2025-03-19 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeMAR/07</t>
+          <t>Interest Rate Projection - Longer</t>
         </is>
       </c>
       <c r="C925" t="inlineStr"/>
-      <c r="D925" t="inlineStr"/>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
       <c r="E925" t="inlineStr"/>
       <c r="F925" t="inlineStr"/>
       <c r="G925" t="n">
@@ -26560,12 +26344,12 @@
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>2025-03-12 20:00:00+05:30</t>
+          <t>2025-03-20 00:00:00+05:30</t>
         </is>
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeMAR/07</t>
+          <t>Fed Press Conference</t>
         </is>
       </c>
       <c r="C926" t="inlineStr"/>
@@ -26573,79 +26357,95 @@
       <c r="E926" t="inlineStr"/>
       <c r="F926" t="inlineStr"/>
       <c r="G926" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>2025-03-12 20:00:00+05:30</t>
+          <t>2025-03-20 01:30:00+05:30</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeMAR/07</t>
+          <t>Net Long-term TIC FlowsJAN</t>
         </is>
       </c>
       <c r="C927" t="inlineStr"/>
-      <c r="D927" t="inlineStr"/>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>$72B</t>
+        </is>
+      </c>
       <c r="E927" t="inlineStr"/>
       <c r="F927" t="inlineStr"/>
       <c r="G927" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>2025-03-12 20:00:00+05:30</t>
+          <t>2025-03-20 01:30:00+05:30</t>
         </is>
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeMAR/07</t>
+          <t>Foreign Bond InvestmentJAN</t>
         </is>
       </c>
       <c r="C928" t="inlineStr"/>
-      <c r="D928" t="inlineStr"/>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>$-49.7B</t>
+        </is>
+      </c>
       <c r="E928" t="inlineStr"/>
       <c r="F928" t="inlineStr"/>
       <c r="G928" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>2025-03-12 20:00:00+05:30</t>
+          <t>2025-03-20 01:30:00+05:30</t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeMAR/07</t>
+          <t>Overall Net Capital FlowsJAN</t>
         </is>
       </c>
       <c r="C929" t="inlineStr"/>
-      <c r="D929" t="inlineStr"/>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>$87.1B</t>
+        </is>
+      </c>
       <c r="E929" t="inlineStr"/>
       <c r="F929" t="inlineStr"/>
       <c r="G929" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>2025-03-12 20:00:00+05:30</t>
+          <t>2025-03-20 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B930" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeMAR/07</t>
+          <t>Philly Fed Business ConditionsMAR</t>
         </is>
       </c>
       <c r="C930" t="inlineStr"/>
-      <c r="D930" t="inlineStr"/>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>27.8</t>
+        </is>
+      </c>
       <c r="E930" t="inlineStr"/>
       <c r="F930" t="inlineStr"/>
       <c r="G930" t="n">
@@ -26655,16 +26455,20 @@
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t>2025-03-12 20:00:00+05:30</t>
+          <t>2025-03-20 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B931" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeMAR/07</t>
+          <t>Philly Fed Prices PaidMAR</t>
         </is>
       </c>
       <c r="C931" t="inlineStr"/>
-      <c r="D931" t="inlineStr"/>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>40.50</t>
+        </is>
+      </c>
       <c r="E931" t="inlineStr"/>
       <c r="F931" t="inlineStr"/>
       <c r="G931" t="n">
@@ -26674,16 +26478,20 @@
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>2025-03-12 20:00:00+05:30</t>
+          <t>2025-03-20 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B932" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeMAR/07</t>
+          <t>Philly Fed New OrdersMAR</t>
         </is>
       </c>
       <c r="C932" t="inlineStr"/>
-      <c r="D932" t="inlineStr"/>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
       <c r="E932" t="inlineStr"/>
       <c r="F932" t="inlineStr"/>
       <c r="G932" t="n">
@@ -26693,16 +26501,20 @@
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t>2025-03-12 20:00:00+05:30</t>
+          <t>2025-03-20 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeMAR/07</t>
+          <t>Philly Fed EmploymentMAR</t>
         </is>
       </c>
       <c r="C933" t="inlineStr"/>
-      <c r="D933" t="inlineStr"/>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
       <c r="E933" t="inlineStr"/>
       <c r="F933" t="inlineStr"/>
       <c r="G933" t="n">
@@ -26712,16 +26524,20 @@
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>2025-03-12 20:00:00+05:30</t>
+          <t>2025-03-20 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B934" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeMAR/07</t>
+          <t>Philly Fed CAPEX IndexMAR</t>
         </is>
       </c>
       <c r="C934" t="inlineStr"/>
-      <c r="D934" t="inlineStr"/>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>14.00</t>
+        </is>
+      </c>
       <c r="E934" t="inlineStr"/>
       <c r="F934" t="inlineStr"/>
       <c r="G934" t="n">
@@ -26731,12 +26547,12 @@
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>2025-03-12 20:00:00+05:30</t>
+          <t>2025-03-20 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeMAR/07</t>
+          <t>Continuing Jobless ClaimsMAR/08</t>
         </is>
       </c>
       <c r="C935" t="inlineStr"/>
@@ -26750,31 +26566,39 @@
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>2025-03-12 20:00:00+05:30</t>
+          <t>2025-03-20 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeMAR/07</t>
+          <t>Philadelphia Fed Manufacturing IndexMAR</t>
         </is>
       </c>
       <c r="C936" t="inlineStr"/>
-      <c r="D936" t="inlineStr"/>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>18.1</t>
+        </is>
+      </c>
       <c r="E936" t="inlineStr"/>
-      <c r="F936" t="inlineStr"/>
+      <c r="F936" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="G936" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>2025-03-12 20:00:00+05:30</t>
+          <t>2025-03-20 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeMAR/07</t>
+          <t>Initial Jobless ClaimsMAR/15</t>
         </is>
       </c>
       <c r="C937" t="inlineStr"/>
@@ -26788,18 +26612,26 @@
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>2025-03-12 20:00:00+05:30</t>
+          <t>2025-03-20 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeMAR/07</t>
+          <t>Current AccountQ4</t>
         </is>
       </c>
       <c r="C938" t="inlineStr"/>
-      <c r="D938" t="inlineStr"/>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>$-310.9B</t>
+        </is>
+      </c>
       <c r="E938" t="inlineStr"/>
-      <c r="F938" t="inlineStr"/>
+      <c r="F938" t="inlineStr">
+        <is>
+          <t>$ -350.0B</t>
+        </is>
+      </c>
       <c r="G938" t="n">
         <v>2</v>
       </c>
@@ -26807,12 +26639,12 @@
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>2025-03-12 21:00:00+05:30</t>
+          <t>2025-03-20 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>Jobless Claims 4-week AverageMAR/15</t>
         </is>
       </c>
       <c r="C939" t="inlineStr"/>
@@ -26826,12 +26658,12 @@
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t>2025-03-12 21:00:00+05:30</t>
+          <t>2025-03-20 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B940" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>CB Leading Index MoMFEB</t>
         </is>
       </c>
       <c r="C940" t="inlineStr"/>
@@ -26845,166 +26677,138 @@
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t>2025-03-12 22:30:00+05:30</t>
+          <t>2025-03-20 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t>10-Year Note Auction</t>
+          <t>Existing Home SalesFEB</t>
         </is>
       </c>
       <c r="C941" t="inlineStr"/>
       <c r="D941" t="inlineStr">
         <is>
-          <t>4.632%</t>
+          <t>4.08M</t>
         </is>
       </c>
       <c r="E941" t="inlineStr"/>
       <c r="F941" t="inlineStr"/>
       <c r="G941" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>2025-03-12 22:30:00+05:30</t>
+          <t>2025-03-20 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B942" t="inlineStr">
         <is>
-          <t>10-Year Note Auction</t>
+          <t>Existing Home Sales MoMFEB</t>
         </is>
       </c>
       <c r="C942" t="inlineStr"/>
       <c r="D942" t="inlineStr">
         <is>
-          <t>4.632%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="E942" t="inlineStr"/>
       <c r="F942" t="inlineStr"/>
       <c r="G942" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>2025-03-12 23:30:00+05:30</t>
+          <t>2025-03-20 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>Monthly Budget StatementFEB</t>
+          <t>EIA Natural Gas Stocks ChangeMAR/14</t>
         </is>
       </c>
       <c r="C943" t="inlineStr"/>
-      <c r="D943" t="inlineStr">
-        <is>
-          <t>$-129B</t>
-        </is>
-      </c>
+      <c r="D943" t="inlineStr"/>
       <c r="E943" t="inlineStr"/>
-      <c r="F943" t="inlineStr">
-        <is>
-          <t>$-90.0B</t>
-        </is>
-      </c>
+      <c r="F943" t="inlineStr"/>
       <c r="G943" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>2025-03-12 23:30:00+05:30</t>
+          <t>2025-03-20 21:30:00+05:30</t>
         </is>
       </c>
       <c r="B944" t="inlineStr">
         <is>
-          <t>Monthly Budget StatementFEB</t>
+          <t>15-Year Mortgage RateMAR/20</t>
         </is>
       </c>
       <c r="C944" t="inlineStr"/>
-      <c r="D944" t="inlineStr">
-        <is>
-          <t>$-129B</t>
-        </is>
-      </c>
+      <c r="D944" t="inlineStr"/>
       <c r="E944" t="inlineStr"/>
-      <c r="F944" t="inlineStr">
-        <is>
-          <t>$-90.0B</t>
-        </is>
-      </c>
+      <c r="F944" t="inlineStr"/>
       <c r="G944" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>2025-03-13 18:00:00+05:30</t>
+          <t>2025-03-20 21:30:00+05:30</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>PPI MoMFEB</t>
+          <t>30-Year Mortgage RateMAR/20</t>
         </is>
       </c>
       <c r="C945" t="inlineStr"/>
-      <c r="D945" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D945" t="inlineStr"/>
       <c r="E945" t="inlineStr"/>
-      <c r="F945" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="F945" t="inlineStr"/>
       <c r="G945" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>2025-03-13 18:00:00+05:30</t>
+          <t>2025-03-20 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t>Core PPI MoMFEB</t>
+          <t>10-Year TIPS Auction</t>
         </is>
       </c>
       <c r="C946" t="inlineStr"/>
       <c r="D946" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.243%</t>
         </is>
       </c>
       <c r="E946" t="inlineStr"/>
-      <c r="F946" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="F946" t="inlineStr"/>
       <c r="G946" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>2025-03-13 18:00:00+05:30</t>
+          <t>2025-03-21 02:00:00+05:30</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsMAR/08</t>
+          <t>Fed Balance SheetMAR/19</t>
         </is>
       </c>
       <c r="C947" t="inlineStr"/>
@@ -27012,18 +26816,18 @@
       <c r="E947" t="inlineStr"/>
       <c r="F947" t="inlineStr"/>
       <c r="G947" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t>2025-03-13 18:00:00+05:30</t>
+          <t>2025-03-21 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B948" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsMAR/01</t>
+          <t>Baker Hughes Oil Rig CountMAR/21</t>
         </is>
       </c>
       <c r="C948" t="inlineStr"/>
@@ -27037,26 +26841,18 @@
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t>2025-03-13 18:00:00+05:30</t>
+          <t>2025-03-21 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B949" t="inlineStr">
         <is>
-          <t>Core PPI YoYFEB</t>
+          <t>Baker Hughes Total Rigs CountMAR/21</t>
         </is>
       </c>
       <c r="C949" t="inlineStr"/>
-      <c r="D949" t="inlineStr">
-        <is>
-          <t>3.6%</t>
-        </is>
-      </c>
+      <c r="D949" t="inlineStr"/>
       <c r="E949" t="inlineStr"/>
-      <c r="F949" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
+      <c r="F949" t="inlineStr"/>
       <c r="G949" t="n">
         <v>3</v>
       </c>
@@ -27064,2662 +26860,27 @@
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t>2025-03-13 18:00:00+05:30</t>
+          <t>2025-03-24 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B950" t="inlineStr">
         <is>
-          <t>PPIFEB</t>
+          <t>Chicago Fed National Activity IndexFEB</t>
         </is>
       </c>
       <c r="C950" t="inlineStr"/>
       <c r="D950" t="inlineStr">
         <is>
-          <t>147.716</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="E950" t="inlineStr"/>
       <c r="F950" t="inlineStr">
         <is>
-          <t>148.2</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="G950" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="951">
-      <c r="A951" t="inlineStr">
-        <is>
-          <t>2025-03-13 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B951" t="inlineStr">
-        <is>
-          <t>PPI Ex Food, Energy and Trade MoMFEB</t>
-        </is>
-      </c>
-      <c r="C951" t="inlineStr"/>
-      <c r="D951" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E951" t="inlineStr"/>
-      <c r="F951" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="G951" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="952">
-      <c r="A952" t="inlineStr">
-        <is>
-          <t>2025-03-13 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B952" t="inlineStr">
-        <is>
-          <t>PPI Ex Food, Energy and Trade YoYFEB</t>
-        </is>
-      </c>
-      <c r="C952" t="inlineStr"/>
-      <c r="D952" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
-      <c r="E952" t="inlineStr"/>
-      <c r="F952" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="G952" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="953">
-      <c r="A953" t="inlineStr">
-        <is>
-          <t>2025-03-13 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B953" t="inlineStr">
-        <is>
-          <t>PPI YoYFEB</t>
-        </is>
-      </c>
-      <c r="C953" t="inlineStr"/>
-      <c r="D953" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E953" t="inlineStr"/>
-      <c r="F953" t="inlineStr">
-        <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="G953" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="954">
-      <c r="A954" t="inlineStr">
-        <is>
-          <t>2025-03-13 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B954" t="inlineStr">
-        <is>
-          <t>Jobless Claims 4-week AverageMAR/08</t>
-        </is>
-      </c>
-      <c r="C954" t="inlineStr"/>
-      <c r="D954" t="inlineStr"/>
-      <c r="E954" t="inlineStr"/>
-      <c r="F954" t="inlineStr"/>
-      <c r="G954" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="955">
-      <c r="A955" t="inlineStr">
-        <is>
-          <t>2025-03-13 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B955" t="inlineStr">
-        <is>
-          <t>PPI YoYFEB</t>
-        </is>
-      </c>
-      <c r="C955" t="inlineStr"/>
-      <c r="D955" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E955" t="inlineStr"/>
-      <c r="F955" t="inlineStr">
-        <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="G955" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="956">
-      <c r="A956" t="inlineStr">
-        <is>
-          <t>2025-03-13 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B956" t="inlineStr">
-        <is>
-          <t>PPI Ex Food, Energy and Trade YoYFEB</t>
-        </is>
-      </c>
-      <c r="C956" t="inlineStr"/>
-      <c r="D956" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
-      <c r="E956" t="inlineStr"/>
-      <c r="F956" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="G956" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="957">
-      <c r="A957" t="inlineStr">
-        <is>
-          <t>2025-03-13 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B957" t="inlineStr">
-        <is>
-          <t>Continuing Jobless ClaimsMAR/01</t>
-        </is>
-      </c>
-      <c r="C957" t="inlineStr"/>
-      <c r="D957" t="inlineStr"/>
-      <c r="E957" t="inlineStr"/>
-      <c r="F957" t="inlineStr"/>
-      <c r="G957" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="958">
-      <c r="A958" t="inlineStr">
-        <is>
-          <t>2025-03-13 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B958" t="inlineStr">
-        <is>
-          <t>Jobless Claims 4-week AverageMAR/08</t>
-        </is>
-      </c>
-      <c r="C958" t="inlineStr"/>
-      <c r="D958" t="inlineStr"/>
-      <c r="E958" t="inlineStr"/>
-      <c r="F958" t="inlineStr"/>
-      <c r="G958" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="959">
-      <c r="A959" t="inlineStr">
-        <is>
-          <t>2025-03-13 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B959" t="inlineStr">
-        <is>
-          <t>PPI MoMFEB</t>
-        </is>
-      </c>
-      <c r="C959" t="inlineStr"/>
-      <c r="D959" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E959" t="inlineStr"/>
-      <c r="F959" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="G959" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="960">
-      <c r="A960" t="inlineStr">
-        <is>
-          <t>2025-03-13 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B960" t="inlineStr">
-        <is>
-          <t>PPIFEB</t>
-        </is>
-      </c>
-      <c r="C960" t="inlineStr"/>
-      <c r="D960" t="inlineStr">
-        <is>
-          <t>147.716</t>
-        </is>
-      </c>
-      <c r="E960" t="inlineStr"/>
-      <c r="F960" t="inlineStr">
-        <is>
-          <t>148.2</t>
-        </is>
-      </c>
-      <c r="G960" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="961">
-      <c r="A961" t="inlineStr">
-        <is>
-          <t>2025-03-13 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B961" t="inlineStr">
-        <is>
-          <t>Core PPI YoYFEB</t>
-        </is>
-      </c>
-      <c r="C961" t="inlineStr"/>
-      <c r="D961" t="inlineStr">
-        <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="E961" t="inlineStr"/>
-      <c r="F961" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="G961" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="962">
-      <c r="A962" t="inlineStr">
-        <is>
-          <t>2025-03-13 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B962" t="inlineStr">
-        <is>
-          <t>PPI Ex Food, Energy and Trade MoMFEB</t>
-        </is>
-      </c>
-      <c r="C962" t="inlineStr"/>
-      <c r="D962" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E962" t="inlineStr"/>
-      <c r="F962" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="G962" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="963">
-      <c r="A963" t="inlineStr">
-        <is>
-          <t>2025-03-13 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B963" t="inlineStr">
-        <is>
-          <t>Initial Jobless ClaimsMAR/08</t>
-        </is>
-      </c>
-      <c r="C963" t="inlineStr"/>
-      <c r="D963" t="inlineStr"/>
-      <c r="E963" t="inlineStr"/>
-      <c r="F963" t="inlineStr"/>
-      <c r="G963" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="964">
-      <c r="A964" t="inlineStr">
-        <is>
-          <t>2025-03-13 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B964" t="inlineStr">
-        <is>
-          <t>Core PPI MoMFEB</t>
-        </is>
-      </c>
-      <c r="C964" t="inlineStr"/>
-      <c r="D964" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E964" t="inlineStr"/>
-      <c r="F964" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="G964" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="965">
-      <c r="A965" t="inlineStr">
-        <is>
-          <t>2025-03-13 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B965" t="inlineStr">
-        <is>
-          <t>EIA Natural Gas Stocks ChangeMAR/07</t>
-        </is>
-      </c>
-      <c r="C965" t="inlineStr"/>
-      <c r="D965" t="inlineStr"/>
-      <c r="E965" t="inlineStr"/>
-      <c r="F965" t="inlineStr"/>
-      <c r="G965" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="966">
-      <c r="A966" t="inlineStr">
-        <is>
-          <t>2025-03-13 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B966" t="inlineStr">
-        <is>
-          <t>EIA Natural Gas Stocks ChangeMAR/07</t>
-        </is>
-      </c>
-      <c r="C966" t="inlineStr"/>
-      <c r="D966" t="inlineStr"/>
-      <c r="E966" t="inlineStr"/>
-      <c r="F966" t="inlineStr"/>
-      <c r="G966" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="967">
-      <c r="A967" t="inlineStr">
-        <is>
-          <t>2025-03-13 21:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B967" t="inlineStr">
-        <is>
-          <t>4-Week Bill Auction</t>
-        </is>
-      </c>
-      <c r="C967" t="inlineStr"/>
-      <c r="D967" t="inlineStr"/>
-      <c r="E967" t="inlineStr"/>
-      <c r="F967" t="inlineStr"/>
-      <c r="G967" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="968">
-      <c r="A968" t="inlineStr">
-        <is>
-          <t>2025-03-13 21:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B968" t="inlineStr">
-        <is>
-          <t>8-Week Bill Auction</t>
-        </is>
-      </c>
-      <c r="C968" t="inlineStr"/>
-      <c r="D968" t="inlineStr"/>
-      <c r="E968" t="inlineStr"/>
-      <c r="F968" t="inlineStr"/>
-      <c r="G968" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="969">
-      <c r="A969" t="inlineStr">
-        <is>
-          <t>2025-03-13 21:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B969" t="inlineStr">
-        <is>
-          <t>8-Week Bill Auction</t>
-        </is>
-      </c>
-      <c r="C969" t="inlineStr"/>
-      <c r="D969" t="inlineStr"/>
-      <c r="E969" t="inlineStr"/>
-      <c r="F969" t="inlineStr"/>
-      <c r="G969" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="970">
-      <c r="A970" t="inlineStr">
-        <is>
-          <t>2025-03-13 21:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B970" t="inlineStr">
-        <is>
-          <t>4-Week Bill Auction</t>
-        </is>
-      </c>
-      <c r="C970" t="inlineStr"/>
-      <c r="D970" t="inlineStr"/>
-      <c r="E970" t="inlineStr"/>
-      <c r="F970" t="inlineStr"/>
-      <c r="G970" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="971">
-      <c r="A971" t="inlineStr">
-        <is>
-          <t>2025-03-13 21:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B971" t="inlineStr">
-        <is>
-          <t>30-Year Mortgage RateMAR/13</t>
-        </is>
-      </c>
-      <c r="C971" t="inlineStr"/>
-      <c r="D971" t="inlineStr"/>
-      <c r="E971" t="inlineStr"/>
-      <c r="F971" t="inlineStr"/>
-      <c r="G971" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="972">
-      <c r="A972" t="inlineStr">
-        <is>
-          <t>2025-03-13 21:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B972" t="inlineStr">
-        <is>
-          <t>15-Year Mortgage RateMAR/13</t>
-        </is>
-      </c>
-      <c r="C972" t="inlineStr"/>
-      <c r="D972" t="inlineStr"/>
-      <c r="E972" t="inlineStr"/>
-      <c r="F972" t="inlineStr"/>
-      <c r="G972" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="973">
-      <c r="A973" t="inlineStr">
-        <is>
-          <t>2025-03-13 21:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B973" t="inlineStr">
-        <is>
-          <t>30-Year Mortgage RateMAR/13</t>
-        </is>
-      </c>
-      <c r="C973" t="inlineStr"/>
-      <c r="D973" t="inlineStr"/>
-      <c r="E973" t="inlineStr"/>
-      <c r="F973" t="inlineStr"/>
-      <c r="G973" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="974">
-      <c r="A974" t="inlineStr">
-        <is>
-          <t>2025-03-13 21:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B974" t="inlineStr">
-        <is>
-          <t>15-Year Mortgage RateMAR/13</t>
-        </is>
-      </c>
-      <c r="C974" t="inlineStr"/>
-      <c r="D974" t="inlineStr"/>
-      <c r="E974" t="inlineStr"/>
-      <c r="F974" t="inlineStr"/>
-      <c r="G974" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="975">
-      <c r="A975" t="inlineStr">
-        <is>
-          <t>2025-03-13 22:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B975" t="inlineStr">
-        <is>
-          <t>30-Year Bond Auction</t>
-        </is>
-      </c>
-      <c r="C975" t="inlineStr"/>
-      <c r="D975" t="inlineStr">
-        <is>
-          <t>4.748%</t>
-        </is>
-      </c>
-      <c r="E975" t="inlineStr"/>
-      <c r="F975" t="inlineStr"/>
-      <c r="G975" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="976">
-      <c r="A976" t="inlineStr">
-        <is>
-          <t>2025-03-13 22:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B976" t="inlineStr">
-        <is>
-          <t>30-Year Bond Auction</t>
-        </is>
-      </c>
-      <c r="C976" t="inlineStr"/>
-      <c r="D976" t="inlineStr">
-        <is>
-          <t>4.748%</t>
-        </is>
-      </c>
-      <c r="E976" t="inlineStr"/>
-      <c r="F976" t="inlineStr"/>
-      <c r="G976" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="977">
-      <c r="A977" t="inlineStr">
-        <is>
-          <t>2025-03-14 02:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B977" t="inlineStr">
-        <is>
-          <t>Fed Balance SheetMAR/12</t>
-        </is>
-      </c>
-      <c r="C977" t="inlineStr"/>
-      <c r="D977" t="inlineStr"/>
-      <c r="E977" t="inlineStr"/>
-      <c r="F977" t="inlineStr"/>
-      <c r="G977" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="978">
-      <c r="A978" t="inlineStr">
-        <is>
-          <t>2025-03-14 02:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B978" t="inlineStr">
-        <is>
-          <t>Fed Balance SheetMAR/12</t>
-        </is>
-      </c>
-      <c r="C978" t="inlineStr"/>
-      <c r="D978" t="inlineStr"/>
-      <c r="E978" t="inlineStr"/>
-      <c r="F978" t="inlineStr"/>
-      <c r="G978" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="979">
-      <c r="A979" t="inlineStr">
-        <is>
-          <t>2025-03-14 19:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B979" t="inlineStr">
-        <is>
-          <t>Michigan 5 Year Inflation Expectations PrelMAR</t>
-        </is>
-      </c>
-      <c r="C979" t="inlineStr"/>
-      <c r="D979" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E979" t="inlineStr"/>
-      <c r="F979" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
-      <c r="G979" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="980">
-      <c r="A980" t="inlineStr">
-        <is>
-          <t>2025-03-14 19:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B980" t="inlineStr">
-        <is>
-          <t>Michigan Consumer Sentiment PrelMAR</t>
-        </is>
-      </c>
-      <c r="C980" t="inlineStr"/>
-      <c r="D980" t="inlineStr"/>
-      <c r="E980" t="inlineStr"/>
-      <c r="F980" t="inlineStr">
-        <is>
-          <t>67.2</t>
-        </is>
-      </c>
-      <c r="G980" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="981">
-      <c r="A981" t="inlineStr">
-        <is>
-          <t>2025-03-14 19:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B981" t="inlineStr">
-        <is>
-          <t>Michigan Inflation Expectations PrelMAR</t>
-        </is>
-      </c>
-      <c r="C981" t="inlineStr"/>
-      <c r="D981" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="E981" t="inlineStr"/>
-      <c r="F981" t="inlineStr">
-        <is>
-          <t>4.4%</t>
-        </is>
-      </c>
-      <c r="G981" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="982">
-      <c r="A982" t="inlineStr">
-        <is>
-          <t>2025-03-14 19:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B982" t="inlineStr">
-        <is>
-          <t>Michigan Current Conditions PrelMAR</t>
-        </is>
-      </c>
-      <c r="C982" t="inlineStr"/>
-      <c r="D982" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="E982" t="inlineStr"/>
-      <c r="F982" t="inlineStr">
-        <is>
-          <t>68.4</t>
-        </is>
-      </c>
-      <c r="G982" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="983">
-      <c r="A983" t="inlineStr">
-        <is>
-          <t>2025-03-14 19:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B983" t="inlineStr">
-        <is>
-          <t>Michigan Current Conditions PrelMAR</t>
-        </is>
-      </c>
-      <c r="C983" t="inlineStr"/>
-      <c r="D983" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="E983" t="inlineStr"/>
-      <c r="F983" t="inlineStr">
-        <is>
-          <t>68.4</t>
-        </is>
-      </c>
-      <c r="G983" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="984">
-      <c r="A984" t="inlineStr">
-        <is>
-          <t>2025-03-14 19:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B984" t="inlineStr">
-        <is>
-          <t>Michigan Inflation Expectations PrelMAR</t>
-        </is>
-      </c>
-      <c r="C984" t="inlineStr"/>
-      <c r="D984" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="E984" t="inlineStr"/>
-      <c r="F984" t="inlineStr">
-        <is>
-          <t>4.4%</t>
-        </is>
-      </c>
-      <c r="G984" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="985">
-      <c r="A985" t="inlineStr">
-        <is>
-          <t>2025-03-14 19:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B985" t="inlineStr">
-        <is>
-          <t>Michigan 5 Year Inflation Expectations PrelMAR</t>
-        </is>
-      </c>
-      <c r="C985" t="inlineStr"/>
-      <c r="D985" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E985" t="inlineStr"/>
-      <c r="F985" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
-      <c r="G985" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="986">
-      <c r="A986" t="inlineStr">
-        <is>
-          <t>2025-03-14 19:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B986" t="inlineStr">
-        <is>
-          <t>Michigan Consumer Sentiment PrelMAR</t>
-        </is>
-      </c>
-      <c r="C986" t="inlineStr"/>
-      <c r="D986" t="inlineStr"/>
-      <c r="E986" t="inlineStr"/>
-      <c r="F986" t="inlineStr">
-        <is>
-          <t>67.2</t>
-        </is>
-      </c>
-      <c r="G986" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="987">
-      <c r="A987" t="inlineStr">
-        <is>
-          <t>2025-03-14 19:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B987" t="inlineStr">
-        <is>
-          <t>Michigan Consumer Expectations PrelMAR</t>
-        </is>
-      </c>
-      <c r="C987" t="inlineStr"/>
-      <c r="D987" t="inlineStr"/>
-      <c r="E987" t="inlineStr"/>
-      <c r="F987" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="G987" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="988">
-      <c r="A988" t="inlineStr">
-        <is>
-          <t>2025-03-14 19:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B988" t="inlineStr">
-        <is>
-          <t>Michigan Consumer Expectations PrelMAR</t>
-        </is>
-      </c>
-      <c r="C988" t="inlineStr"/>
-      <c r="D988" t="inlineStr"/>
-      <c r="E988" t="inlineStr"/>
-      <c r="F988" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="G988" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="989">
-      <c r="A989" t="inlineStr">
-        <is>
-          <t>2025-03-14 22:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B989" t="inlineStr">
-        <is>
-          <t>Baker Hughes Oil Rig CountMAR/14</t>
-        </is>
-      </c>
-      <c r="C989" t="inlineStr"/>
-      <c r="D989" t="inlineStr"/>
-      <c r="E989" t="inlineStr"/>
-      <c r="F989" t="inlineStr"/>
-      <c r="G989" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="990">
-      <c r="A990" t="inlineStr">
-        <is>
-          <t>2025-03-14 22:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B990" t="inlineStr">
-        <is>
-          <t>Baker Hughes Total Rigs CountMAR/14</t>
-        </is>
-      </c>
-      <c r="C990" t="inlineStr"/>
-      <c r="D990" t="inlineStr"/>
-      <c r="E990" t="inlineStr"/>
-      <c r="F990" t="inlineStr"/>
-      <c r="G990" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="991">
-      <c r="A991" t="inlineStr">
-        <is>
-          <t>2025-03-14 22:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B991" t="inlineStr">
-        <is>
-          <t>Baker Hughes Total Rigs CountMAR/14</t>
-        </is>
-      </c>
-      <c r="C991" t="inlineStr"/>
-      <c r="D991" t="inlineStr"/>
-      <c r="E991" t="inlineStr"/>
-      <c r="F991" t="inlineStr"/>
-      <c r="G991" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="992">
-      <c r="A992" t="inlineStr">
-        <is>
-          <t>2025-03-14 22:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B992" t="inlineStr">
-        <is>
-          <t>Baker Hughes Oil Rig CountMAR/14</t>
-        </is>
-      </c>
-      <c r="C992" t="inlineStr"/>
-      <c r="D992" t="inlineStr"/>
-      <c r="E992" t="inlineStr"/>
-      <c r="F992" t="inlineStr"/>
-      <c r="G992" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="993">
-      <c r="A993" t="inlineStr">
-        <is>
-          <t>2025-03-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B993" t="inlineStr">
-        <is>
-          <t>Retail Sales MoMFEB</t>
-        </is>
-      </c>
-      <c r="C993" t="inlineStr"/>
-      <c r="D993" t="inlineStr">
-        <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="E993" t="inlineStr"/>
-      <c r="F993" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="G993" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="994">
-      <c r="A994" t="inlineStr">
-        <is>
-          <t>2025-03-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B994" t="inlineStr">
-        <is>
-          <t>NY Empire State Manufacturing IndexMAR</t>
-        </is>
-      </c>
-      <c r="C994" t="inlineStr"/>
-      <c r="D994" t="inlineStr">
-        <is>
-          <t>5.7</t>
-        </is>
-      </c>
-      <c r="E994" t="inlineStr"/>
-      <c r="F994" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G994" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="995">
-      <c r="A995" t="inlineStr">
-        <is>
-          <t>2025-03-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B995" t="inlineStr">
-        <is>
-          <t>Retail Sales Control Group MoMFEB</t>
-        </is>
-      </c>
-      <c r="C995" t="inlineStr"/>
-      <c r="D995" t="inlineStr">
-        <is>
-          <t>-0.8%</t>
-        </is>
-      </c>
-      <c r="E995" t="inlineStr"/>
-      <c r="F995" t="inlineStr"/>
-      <c r="G995" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="996">
-      <c r="A996" t="inlineStr">
-        <is>
-          <t>2025-03-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B996" t="inlineStr">
-        <is>
-          <t>Retail Sales Ex Autos MoMFEB</t>
-        </is>
-      </c>
-      <c r="C996" t="inlineStr"/>
-      <c r="D996" t="inlineStr">
-        <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="E996" t="inlineStr"/>
-      <c r="F996" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="G996" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="997">
-      <c r="A997" t="inlineStr">
-        <is>
-          <t>2025-03-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B997" t="inlineStr">
-        <is>
-          <t>Retail Sales Ex Gas/Autos MoMFEB</t>
-        </is>
-      </c>
-      <c r="C997" t="inlineStr"/>
-      <c r="D997" t="inlineStr">
-        <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="E997" t="inlineStr"/>
-      <c r="F997" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="G997" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="998">
-      <c r="A998" t="inlineStr">
-        <is>
-          <t>2025-03-17 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B998" t="inlineStr">
-        <is>
-          <t>Retail Sales YoYFEB</t>
-        </is>
-      </c>
-      <c r="C998" t="inlineStr"/>
-      <c r="D998" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="E998" t="inlineStr"/>
-      <c r="F998" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="G998" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="999">
-      <c r="A999" t="inlineStr">
-        <is>
-          <t>2025-03-17 19:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B999" t="inlineStr">
-        <is>
-          <t>Retail Inventories Ex Autos MoMJAN</t>
-        </is>
-      </c>
-      <c r="C999" t="inlineStr"/>
-      <c r="D999" t="inlineStr"/>
-      <c r="E999" t="inlineStr"/>
-      <c r="F999" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="G999" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1000">
-      <c r="A1000" t="inlineStr">
-        <is>
-          <t>2025-03-17 19:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1000" t="inlineStr">
-        <is>
-          <t>NAHB Housing Market IndexMAR</t>
-        </is>
-      </c>
-      <c r="C1000" t="inlineStr"/>
-      <c r="D1000" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="E1000" t="inlineStr"/>
-      <c r="F1000" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="G1000" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="1001">
-      <c r="A1001" t="inlineStr">
-        <is>
-          <t>2025-03-17 19:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1001" t="inlineStr">
-        <is>
-          <t>Business Inventories MoMJAN</t>
-        </is>
-      </c>
-      <c r="C1001" t="inlineStr"/>
-      <c r="D1001" t="inlineStr">
-        <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="E1001" t="inlineStr"/>
-      <c r="F1001" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="G1001" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="1002">
-      <c r="A1002" t="inlineStr">
-        <is>
-          <t>2025-03-17 21:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1002" t="inlineStr">
-        <is>
-          <t>3-Month Bill Auction</t>
-        </is>
-      </c>
-      <c r="C1002" t="inlineStr"/>
-      <c r="D1002" t="inlineStr"/>
-      <c r="E1002" t="inlineStr"/>
-      <c r="F1002" t="inlineStr"/>
-      <c r="G1002" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1003">
-      <c r="A1003" t="inlineStr">
-        <is>
-          <t>2025-03-17 21:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1003" t="inlineStr">
-        <is>
-          <t>6-Month Bill Auction</t>
-        </is>
-      </c>
-      <c r="C1003" t="inlineStr"/>
-      <c r="D1003" t="inlineStr"/>
-      <c r="E1003" t="inlineStr"/>
-      <c r="F1003" t="inlineStr"/>
-      <c r="G1003" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1004">
-      <c r="A1004" t="inlineStr">
-        <is>
-          <t>2025-03-17 21:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1004" t="inlineStr">
-        <is>
-          <t>NOPA Crush Report</t>
-        </is>
-      </c>
-      <c r="C1004" t="inlineStr"/>
-      <c r="D1004" t="inlineStr"/>
-      <c r="E1004" t="inlineStr"/>
-      <c r="F1004" t="inlineStr"/>
-      <c r="G1004" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1005">
-      <c r="A1005" t="inlineStr">
-        <is>
-          <t>2025-03-18 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1005" t="inlineStr">
-        <is>
-          <t>Export Prices YoYFEB</t>
-        </is>
-      </c>
-      <c r="C1005" t="inlineStr"/>
-      <c r="D1005" t="inlineStr">
-        <is>
-          <t>2.7%</t>
-        </is>
-      </c>
-      <c r="E1005" t="inlineStr"/>
-      <c r="F1005" t="inlineStr">
-        <is>
-          <t>3.0%</t>
-        </is>
-      </c>
-      <c r="G1005" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1006">
-      <c r="A1006" t="inlineStr">
-        <is>
-          <t>2025-03-18 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1006" t="inlineStr">
-        <is>
-          <t>Import Prices YoYFEB</t>
-        </is>
-      </c>
-      <c r="C1006" t="inlineStr"/>
-      <c r="D1006" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="E1006" t="inlineStr"/>
-      <c r="F1006" t="inlineStr">
-        <is>
-          <t>3.1%</t>
-        </is>
-      </c>
-      <c r="G1006" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1007">
-      <c r="A1007" t="inlineStr">
-        <is>
-          <t>2025-03-18 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1007" t="inlineStr">
-        <is>
-          <t>Housing Starts MoMFEB</t>
-        </is>
-      </c>
-      <c r="C1007" t="inlineStr"/>
-      <c r="D1007" t="inlineStr">
-        <is>
-          <t>-9.8%</t>
-        </is>
-      </c>
-      <c r="E1007" t="inlineStr"/>
-      <c r="F1007" t="inlineStr">
-        <is>
-          <t>-1.9%</t>
-        </is>
-      </c>
-      <c r="G1007" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="1008">
-      <c r="A1008" t="inlineStr">
-        <is>
-          <t>2025-03-18 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1008" t="inlineStr">
-        <is>
-          <t>Export Prices MoMFEB</t>
-        </is>
-      </c>
-      <c r="C1008" t="inlineStr"/>
-      <c r="D1008" t="inlineStr">
-        <is>
-          <t>1.3%</t>
-        </is>
-      </c>
-      <c r="E1008" t="inlineStr"/>
-      <c r="F1008" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="G1008" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="1009">
-      <c r="A1009" t="inlineStr">
-        <is>
-          <t>2025-03-18 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1009" t="inlineStr">
-        <is>
-          <t>Import Prices MoMFEB</t>
-        </is>
-      </c>
-      <c r="C1009" t="inlineStr"/>
-      <c r="D1009" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E1009" t="inlineStr"/>
-      <c r="F1009" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="G1009" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="1010">
-      <c r="A1010" t="inlineStr">
-        <is>
-          <t>2025-03-18 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1010" t="inlineStr">
-        <is>
-          <t>Housing StartsFEB</t>
-        </is>
-      </c>
-      <c r="C1010" t="inlineStr"/>
-      <c r="D1010" t="inlineStr">
-        <is>
-          <t>1.366M</t>
-        </is>
-      </c>
-      <c r="E1010" t="inlineStr"/>
-      <c r="F1010" t="inlineStr">
-        <is>
-          <t>1.34M</t>
-        </is>
-      </c>
-      <c r="G1010" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1011">
-      <c r="A1011" t="inlineStr">
-        <is>
-          <t>2025-03-18 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1011" t="inlineStr">
-        <is>
-          <t>Building Permits PrelFEB</t>
-        </is>
-      </c>
-      <c r="C1011" t="inlineStr"/>
-      <c r="D1011" t="inlineStr">
-        <is>
-          <t>1.473M</t>
-        </is>
-      </c>
-      <c r="E1011" t="inlineStr"/>
-      <c r="F1011" t="inlineStr"/>
-      <c r="G1011" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1012">
-      <c r="A1012" t="inlineStr">
-        <is>
-          <t>2025-03-18 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1012" t="inlineStr">
-        <is>
-          <t>Building Permits MoM PrelFEB</t>
-        </is>
-      </c>
-      <c r="C1012" t="inlineStr"/>
-      <c r="D1012" t="inlineStr">
-        <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
-      <c r="E1012" t="inlineStr"/>
-      <c r="F1012" t="inlineStr"/>
-      <c r="G1012" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="1013">
-      <c r="A1013" t="inlineStr">
-        <is>
-          <t>2025-03-18 18:25:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1013" t="inlineStr">
-        <is>
-          <t>Redbook YoYMAR/15</t>
-        </is>
-      </c>
-      <c r="C1013" t="inlineStr"/>
-      <c r="D1013" t="inlineStr"/>
-      <c r="E1013" t="inlineStr"/>
-      <c r="F1013" t="inlineStr"/>
-      <c r="G1013" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1014">
-      <c r="A1014" t="inlineStr">
-        <is>
-          <t>2025-03-18 18:45:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1014" t="inlineStr">
-        <is>
-          <t>Industrial Production MoMFEB</t>
-        </is>
-      </c>
-      <c r="C1014" t="inlineStr"/>
-      <c r="D1014" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E1014" t="inlineStr"/>
-      <c r="F1014" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="G1014" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="1015">
-      <c r="A1015" t="inlineStr">
-        <is>
-          <t>2025-03-18 18:45:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1015" t="inlineStr">
-        <is>
-          <t>Capacity UtilizationFEB</t>
-        </is>
-      </c>
-      <c r="C1015" t="inlineStr"/>
-      <c r="D1015" t="inlineStr">
-        <is>
-          <t>77.8%</t>
-        </is>
-      </c>
-      <c r="E1015" t="inlineStr"/>
-      <c r="F1015" t="inlineStr">
-        <is>
-          <t>77.7%</t>
-        </is>
-      </c>
-      <c r="G1015" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1016">
-      <c r="A1016" t="inlineStr">
-        <is>
-          <t>2025-03-18 18:45:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1016" t="inlineStr">
-        <is>
-          <t>Industrial Production YoYFEB</t>
-        </is>
-      </c>
-      <c r="C1016" t="inlineStr"/>
-      <c r="D1016" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="E1016" t="inlineStr"/>
-      <c r="F1016" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="G1016" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1017">
-      <c r="A1017" t="inlineStr">
-        <is>
-          <t>2025-03-18 18:45:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1017" t="inlineStr">
-        <is>
-          <t>Manufacturing Production MoMFEB</t>
-        </is>
-      </c>
-      <c r="C1017" t="inlineStr"/>
-      <c r="D1017" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E1017" t="inlineStr"/>
-      <c r="F1017" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="G1017" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1018">
-      <c r="A1018" t="inlineStr">
-        <is>
-          <t>2025-03-18 18:45:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1018" t="inlineStr">
-        <is>
-          <t>Manufacturing Production YoYFEB</t>
-        </is>
-      </c>
-      <c r="C1018" t="inlineStr"/>
-      <c r="D1018" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="E1018" t="inlineStr"/>
-      <c r="F1018" t="inlineStr">
-        <is>
-          <t>1.3%</t>
-        </is>
-      </c>
-      <c r="G1018" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1019">
-      <c r="A1019" t="inlineStr">
-        <is>
-          <t>2025-03-18 21:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1019" t="inlineStr">
-        <is>
-          <t>52-Week Bill Auction</t>
-        </is>
-      </c>
-      <c r="C1019" t="inlineStr"/>
-      <c r="D1019" t="inlineStr">
-        <is>
-          <t>4.05%</t>
-        </is>
-      </c>
-      <c r="E1019" t="inlineStr"/>
-      <c r="F1019" t="inlineStr"/>
-      <c r="G1019" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1020">
-      <c r="A1020" t="inlineStr">
-        <is>
-          <t>2025-03-18 22:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1020" t="inlineStr">
-        <is>
-          <t>20-Year Bond Auction</t>
-        </is>
-      </c>
-      <c r="C1020" t="inlineStr"/>
-      <c r="D1020" t="inlineStr">
-        <is>
-          <t>4.83%</t>
-        </is>
-      </c>
-      <c r="E1020" t="inlineStr"/>
-      <c r="F1020" t="inlineStr"/>
-      <c r="G1020" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1021">
-      <c r="A1021" t="inlineStr">
-        <is>
-          <t>2025-03-19 02:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1021" t="inlineStr">
-        <is>
-          <t>API Crude Oil Stock ChangeMAR/14</t>
-        </is>
-      </c>
-      <c r="C1021" t="inlineStr"/>
-      <c r="D1021" t="inlineStr"/>
-      <c r="E1021" t="inlineStr"/>
-      <c r="F1021" t="inlineStr"/>
-      <c r="G1021" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="1022">
-      <c r="A1022" t="inlineStr">
-        <is>
-          <t>2025-03-19 16:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1022" t="inlineStr">
-        <is>
-          <t>MBA 30-Year Mortgage RateMAR/14</t>
-        </is>
-      </c>
-      <c r="C1022" t="inlineStr"/>
-      <c r="D1022" t="inlineStr"/>
-      <c r="E1022" t="inlineStr"/>
-      <c r="F1022" t="inlineStr"/>
-      <c r="G1022" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="1023">
-      <c r="A1023" t="inlineStr">
-        <is>
-          <t>2025-03-19 16:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1023" t="inlineStr">
-        <is>
-          <t>MBA Mortgage ApplicationsMAR/14</t>
-        </is>
-      </c>
-      <c r="C1023" t="inlineStr"/>
-      <c r="D1023" t="inlineStr"/>
-      <c r="E1023" t="inlineStr"/>
-      <c r="F1023" t="inlineStr"/>
-      <c r="G1023" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1024">
-      <c r="A1024" t="inlineStr">
-        <is>
-          <t>2025-03-19 16:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1024" t="inlineStr">
-        <is>
-          <t>MBA Mortgage Market IndexMAR/14</t>
-        </is>
-      </c>
-      <c r="C1024" t="inlineStr"/>
-      <c r="D1024" t="inlineStr"/>
-      <c r="E1024" t="inlineStr"/>
-      <c r="F1024" t="inlineStr"/>
-      <c r="G1024" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1025">
-      <c r="A1025" t="inlineStr">
-        <is>
-          <t>2025-03-19 16:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1025" t="inlineStr">
-        <is>
-          <t>MBA Mortgage Refinance IndexMAR/14</t>
-        </is>
-      </c>
-      <c r="C1025" t="inlineStr"/>
-      <c r="D1025" t="inlineStr"/>
-      <c r="E1025" t="inlineStr"/>
-      <c r="F1025" t="inlineStr"/>
-      <c r="G1025" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1026">
-      <c r="A1026" t="inlineStr">
-        <is>
-          <t>2025-03-19 16:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1026" t="inlineStr">
-        <is>
-          <t>MBA Purchase IndexMAR/14</t>
-        </is>
-      </c>
-      <c r="C1026" t="inlineStr"/>
-      <c r="D1026" t="inlineStr"/>
-      <c r="E1026" t="inlineStr"/>
-      <c r="F1026" t="inlineStr"/>
-      <c r="G1026" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1027">
-      <c r="A1027" t="inlineStr">
-        <is>
-          <t>2025-03-19 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1027" t="inlineStr">
-        <is>
-          <t>EIA Heating Oil Stocks ChangeMAR/14</t>
-        </is>
-      </c>
-      <c r="C1027" t="inlineStr"/>
-      <c r="D1027" t="inlineStr"/>
-      <c r="E1027" t="inlineStr"/>
-      <c r="F1027" t="inlineStr"/>
-      <c r="G1027" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1028">
-      <c r="A1028" t="inlineStr">
-        <is>
-          <t>2025-03-19 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1028" t="inlineStr">
-        <is>
-          <t>EIA Gasoline Production ChangeMAR/14</t>
-        </is>
-      </c>
-      <c r="C1028" t="inlineStr"/>
-      <c r="D1028" t="inlineStr"/>
-      <c r="E1028" t="inlineStr"/>
-      <c r="F1028" t="inlineStr"/>
-      <c r="G1028" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1029">
-      <c r="A1029" t="inlineStr">
-        <is>
-          <t>2025-03-19 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1029" t="inlineStr">
-        <is>
-          <t>EIA Distillate Stocks ChangeMAR/14</t>
-        </is>
-      </c>
-      <c r="C1029" t="inlineStr"/>
-      <c r="D1029" t="inlineStr"/>
-      <c r="E1029" t="inlineStr"/>
-      <c r="F1029" t="inlineStr"/>
-      <c r="G1029" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1030">
-      <c r="A1030" t="inlineStr">
-        <is>
-          <t>2025-03-19 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1030" t="inlineStr">
-        <is>
-          <t>EIA Refinery Crude Runs ChangeMAR/14</t>
-        </is>
-      </c>
-      <c r="C1030" t="inlineStr"/>
-      <c r="D1030" t="inlineStr"/>
-      <c r="E1030" t="inlineStr"/>
-      <c r="F1030" t="inlineStr"/>
-      <c r="G1030" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1031">
-      <c r="A1031" t="inlineStr">
-        <is>
-          <t>2025-03-19 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1031" t="inlineStr">
-        <is>
-          <t>EIA Distillate Fuel Production ChangeMAR/14</t>
-        </is>
-      </c>
-      <c r="C1031" t="inlineStr"/>
-      <c r="D1031" t="inlineStr"/>
-      <c r="E1031" t="inlineStr"/>
-      <c r="F1031" t="inlineStr"/>
-      <c r="G1031" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1032">
-      <c r="A1032" t="inlineStr">
-        <is>
-          <t>2025-03-19 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1032" t="inlineStr">
-        <is>
-          <t>EIA Crude Oil Imports ChangeMAR/14</t>
-        </is>
-      </c>
-      <c r="C1032" t="inlineStr"/>
-      <c r="D1032" t="inlineStr"/>
-      <c r="E1032" t="inlineStr"/>
-      <c r="F1032" t="inlineStr"/>
-      <c r="G1032" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1033">
-      <c r="A1033" t="inlineStr">
-        <is>
-          <t>2025-03-19 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1033" t="inlineStr">
-        <is>
-          <t>EIA Gasoline Stocks ChangeMAR/14</t>
-        </is>
-      </c>
-      <c r="C1033" t="inlineStr"/>
-      <c r="D1033" t="inlineStr"/>
-      <c r="E1033" t="inlineStr"/>
-      <c r="F1033" t="inlineStr"/>
-      <c r="G1033" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="1034">
-      <c r="A1034" t="inlineStr">
-        <is>
-          <t>2025-03-19 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1034" t="inlineStr">
-        <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeMAR/14</t>
-        </is>
-      </c>
-      <c r="C1034" t="inlineStr"/>
-      <c r="D1034" t="inlineStr"/>
-      <c r="E1034" t="inlineStr"/>
-      <c r="F1034" t="inlineStr"/>
-      <c r="G1034" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1035">
-      <c r="A1035" t="inlineStr">
-        <is>
-          <t>2025-03-19 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1035" t="inlineStr">
-        <is>
-          <t>EIA Crude Oil Stocks ChangeMAR/14</t>
-        </is>
-      </c>
-      <c r="C1035" t="inlineStr"/>
-      <c r="D1035" t="inlineStr"/>
-      <c r="E1035" t="inlineStr"/>
-      <c r="F1035" t="inlineStr"/>
-      <c r="G1035" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="1036">
-      <c r="A1036" t="inlineStr">
-        <is>
-          <t>2025-03-19 23:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1036" t="inlineStr">
-        <is>
-          <t>Interest Rate Projection - Current</t>
-        </is>
-      </c>
-      <c r="C1036" t="inlineStr"/>
-      <c r="D1036" t="inlineStr">
-        <is>
-          <t>4.4%</t>
-        </is>
-      </c>
-      <c r="E1036" t="inlineStr"/>
-      <c r="F1036" t="inlineStr"/>
-      <c r="G1036" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1037">
-      <c r="A1037" t="inlineStr">
-        <is>
-          <t>2025-03-19 23:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1037" t="inlineStr">
-        <is>
-          <t>Interest Rate Projection - 2nd Yr</t>
-        </is>
-      </c>
-      <c r="C1037" t="inlineStr"/>
-      <c r="D1037" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
-      <c r="E1037" t="inlineStr"/>
-      <c r="F1037" t="inlineStr"/>
-      <c r="G1037" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1038">
-      <c r="A1038" t="inlineStr">
-        <is>
-          <t>2025-03-19 23:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1038" t="inlineStr">
-        <is>
-          <t>International Monetary Market (IMM) Date</t>
-        </is>
-      </c>
-      <c r="C1038" t="inlineStr"/>
-      <c r="D1038" t="inlineStr"/>
-      <c r="E1038" t="inlineStr"/>
-      <c r="F1038" t="inlineStr"/>
-      <c r="G1038" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1039">
-      <c r="A1039" t="inlineStr">
-        <is>
-          <t>2025-03-19 23:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1039" t="inlineStr">
-        <is>
-          <t>FOMC Economic Projections</t>
-        </is>
-      </c>
-      <c r="C1039" t="inlineStr"/>
-      <c r="D1039" t="inlineStr"/>
-      <c r="E1039" t="inlineStr"/>
-      <c r="F1039" t="inlineStr"/>
-      <c r="G1039" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1040">
-      <c r="A1040" t="inlineStr">
-        <is>
-          <t>2025-03-19 23:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1040" t="inlineStr">
-        <is>
-          <t>Fed Interest Rate Decision</t>
-        </is>
-      </c>
-      <c r="C1040" t="inlineStr"/>
-      <c r="D1040" t="inlineStr">
-        <is>
-          <t>4.5%</t>
-        </is>
-      </c>
-      <c r="E1040" t="inlineStr"/>
-      <c r="F1040" t="inlineStr">
-        <is>
-          <t>4.5%</t>
-        </is>
-      </c>
-      <c r="G1040" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1041">
-      <c r="A1041" t="inlineStr">
-        <is>
-          <t>2025-03-19 23:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1041" t="inlineStr">
-        <is>
-          <t>Interest Rate Projection - 1st Yr</t>
-        </is>
-      </c>
-      <c r="C1041" t="inlineStr"/>
-      <c r="D1041" t="inlineStr">
-        <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="E1041" t="inlineStr"/>
-      <c r="F1041" t="inlineStr"/>
-      <c r="G1041" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1042">
-      <c r="A1042" t="inlineStr">
-        <is>
-          <t>2025-03-19 23:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1042" t="inlineStr">
-        <is>
-          <t>Interest Rate Projection - Longer</t>
-        </is>
-      </c>
-      <c r="C1042" t="inlineStr"/>
-      <c r="D1042" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="E1042" t="inlineStr"/>
-      <c r="F1042" t="inlineStr"/>
-      <c r="G1042" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1043">
-      <c r="A1043" t="inlineStr">
-        <is>
-          <t>2025-03-20 00:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1043" t="inlineStr">
-        <is>
-          <t>Fed Press Conference</t>
-        </is>
-      </c>
-      <c r="C1043" t="inlineStr"/>
-      <c r="D1043" t="inlineStr"/>
-      <c r="E1043" t="inlineStr"/>
-      <c r="F1043" t="inlineStr"/>
-      <c r="G1043" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1044">
-      <c r="A1044" t="inlineStr">
-        <is>
-          <t>2025-03-20 01:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1044" t="inlineStr">
-        <is>
-          <t>Net Long-term TIC FlowsJAN</t>
-        </is>
-      </c>
-      <c r="C1044" t="inlineStr"/>
-      <c r="D1044" t="inlineStr">
-        <is>
-          <t>$72B</t>
-        </is>
-      </c>
-      <c r="E1044" t="inlineStr"/>
-      <c r="F1044" t="inlineStr"/>
-      <c r="G1044" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="1045">
-      <c r="A1045" t="inlineStr">
-        <is>
-          <t>2025-03-20 01:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1045" t="inlineStr">
-        <is>
-          <t>Foreign Bond InvestmentJAN</t>
-        </is>
-      </c>
-      <c r="C1045" t="inlineStr"/>
-      <c r="D1045" t="inlineStr">
-        <is>
-          <t>$-49.7B</t>
-        </is>
-      </c>
-      <c r="E1045" t="inlineStr"/>
-      <c r="F1045" t="inlineStr"/>
-      <c r="G1045" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1046">
-      <c r="A1046" t="inlineStr">
-        <is>
-          <t>2025-03-20 01:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1046" t="inlineStr">
-        <is>
-          <t>Overall Net Capital FlowsJAN</t>
-        </is>
-      </c>
-      <c r="C1046" t="inlineStr"/>
-      <c r="D1046" t="inlineStr">
-        <is>
-          <t>$87.1B</t>
-        </is>
-      </c>
-      <c r="E1046" t="inlineStr"/>
-      <c r="F1046" t="inlineStr"/>
-      <c r="G1046" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1047">
-      <c r="A1047" t="inlineStr">
-        <is>
-          <t>2025-03-20 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1047" t="inlineStr">
-        <is>
-          <t>Philly Fed Business ConditionsMAR</t>
-        </is>
-      </c>
-      <c r="C1047" t="inlineStr"/>
-      <c r="D1047" t="inlineStr">
-        <is>
-          <t>27.8</t>
-        </is>
-      </c>
-      <c r="E1047" t="inlineStr"/>
-      <c r="F1047" t="inlineStr"/>
-      <c r="G1047" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1048">
-      <c r="A1048" t="inlineStr">
-        <is>
-          <t>2025-03-20 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1048" t="inlineStr">
-        <is>
-          <t>Philly Fed Prices PaidMAR</t>
-        </is>
-      </c>
-      <c r="C1048" t="inlineStr"/>
-      <c r="D1048" t="inlineStr">
-        <is>
-          <t>40.50</t>
-        </is>
-      </c>
-      <c r="E1048" t="inlineStr"/>
-      <c r="F1048" t="inlineStr"/>
-      <c r="G1048" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1049">
-      <c r="A1049" t="inlineStr">
-        <is>
-          <t>2025-03-20 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1049" t="inlineStr">
-        <is>
-          <t>Philly Fed New OrdersMAR</t>
-        </is>
-      </c>
-      <c r="C1049" t="inlineStr"/>
-      <c r="D1049" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="E1049" t="inlineStr"/>
-      <c r="F1049" t="inlineStr"/>
-      <c r="G1049" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1050">
-      <c r="A1050" t="inlineStr">
-        <is>
-          <t>2025-03-20 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1050" t="inlineStr">
-        <is>
-          <t>Philly Fed EmploymentMAR</t>
-        </is>
-      </c>
-      <c r="C1050" t="inlineStr"/>
-      <c r="D1050" t="inlineStr">
-        <is>
-          <t>5.3</t>
-        </is>
-      </c>
-      <c r="E1050" t="inlineStr"/>
-      <c r="F1050" t="inlineStr"/>
-      <c r="G1050" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1051">
-      <c r="A1051" t="inlineStr">
-        <is>
-          <t>2025-03-20 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1051" t="inlineStr">
-        <is>
-          <t>Philly Fed CAPEX IndexMAR</t>
-        </is>
-      </c>
-      <c r="C1051" t="inlineStr"/>
-      <c r="D1051" t="inlineStr">
-        <is>
-          <t>14.00</t>
-        </is>
-      </c>
-      <c r="E1051" t="inlineStr"/>
-      <c r="F1051" t="inlineStr"/>
-      <c r="G1051" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1052">
-      <c r="A1052" t="inlineStr">
-        <is>
-          <t>2025-03-20 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1052" t="inlineStr">
-        <is>
-          <t>Continuing Jobless ClaimsMAR/08</t>
-        </is>
-      </c>
-      <c r="C1052" t="inlineStr"/>
-      <c r="D1052" t="inlineStr"/>
-      <c r="E1052" t="inlineStr"/>
-      <c r="F1052" t="inlineStr"/>
-      <c r="G1052" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1053">
-      <c r="A1053" t="inlineStr">
-        <is>
-          <t>2025-03-20 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1053" t="inlineStr">
-        <is>
-          <t>Philadelphia Fed Manufacturing IndexMAR</t>
-        </is>
-      </c>
-      <c r="C1053" t="inlineStr"/>
-      <c r="D1053" t="inlineStr">
-        <is>
-          <t>18.1</t>
-        </is>
-      </c>
-      <c r="E1053" t="inlineStr"/>
-      <c r="F1053" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="G1053" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="1054">
-      <c r="A1054" t="inlineStr">
-        <is>
-          <t>2025-03-20 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1054" t="inlineStr">
-        <is>
-          <t>Initial Jobless ClaimsMAR/15</t>
-        </is>
-      </c>
-      <c r="C1054" t="inlineStr"/>
-      <c r="D1054" t="inlineStr"/>
-      <c r="E1054" t="inlineStr"/>
-      <c r="F1054" t="inlineStr"/>
-      <c r="G1054" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="1055">
-      <c r="A1055" t="inlineStr">
-        <is>
-          <t>2025-03-20 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1055" t="inlineStr">
-        <is>
-          <t>Current AccountQ4</t>
-        </is>
-      </c>
-      <c r="C1055" t="inlineStr"/>
-      <c r="D1055" t="inlineStr">
-        <is>
-          <t>$-310.9B</t>
-        </is>
-      </c>
-      <c r="E1055" t="inlineStr"/>
-      <c r="F1055" t="inlineStr">
-        <is>
-          <t>$ -350.0B</t>
-        </is>
-      </c>
-      <c r="G1055" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="1056">
-      <c r="A1056" t="inlineStr">
-        <is>
-          <t>2025-03-20 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1056" t="inlineStr">
-        <is>
-          <t>Jobless Claims 4-week AverageMAR/15</t>
-        </is>
-      </c>
-      <c r="C1056" t="inlineStr"/>
-      <c r="D1056" t="inlineStr"/>
-      <c r="E1056" t="inlineStr"/>
-      <c r="F1056" t="inlineStr"/>
-      <c r="G1056" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1057">
-      <c r="A1057" t="inlineStr">
-        <is>
-          <t>2025-03-20 19:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1057" t="inlineStr">
-        <is>
-          <t>CB Leading Index MoMFEB</t>
-        </is>
-      </c>
-      <c r="C1057" t="inlineStr"/>
-      <c r="D1057" t="inlineStr"/>
-      <c r="E1057" t="inlineStr"/>
-      <c r="F1057" t="inlineStr"/>
-      <c r="G1057" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1058">
-      <c r="A1058" t="inlineStr">
-        <is>
-          <t>2025-03-20 19:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1058" t="inlineStr">
-        <is>
-          <t>Existing Home SalesFEB</t>
-        </is>
-      </c>
-      <c r="C1058" t="inlineStr"/>
-      <c r="D1058" t="inlineStr">
-        <is>
-          <t>4.08M</t>
-        </is>
-      </c>
-      <c r="E1058" t="inlineStr"/>
-      <c r="F1058" t="inlineStr"/>
-      <c r="G1058" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1059">
-      <c r="A1059" t="inlineStr">
-        <is>
-          <t>2025-03-20 19:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1059" t="inlineStr">
-        <is>
-          <t>Existing Home Sales MoMFEB</t>
-        </is>
-      </c>
-      <c r="C1059" t="inlineStr"/>
-      <c r="D1059" t="inlineStr">
-        <is>
-          <t>-4.9%</t>
-        </is>
-      </c>
-      <c r="E1059" t="inlineStr"/>
-      <c r="F1059" t="inlineStr"/>
-      <c r="G1059" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="1060">
-      <c r="A1060" t="inlineStr">
-        <is>
-          <t>2025-03-20 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1060" t="inlineStr">
-        <is>
-          <t>EIA Natural Gas Stocks ChangeMAR/14</t>
-        </is>
-      </c>
-      <c r="C1060" t="inlineStr"/>
-      <c r="D1060" t="inlineStr"/>
-      <c r="E1060" t="inlineStr"/>
-      <c r="F1060" t="inlineStr"/>
-      <c r="G1060" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1061">
-      <c r="A1061" t="inlineStr">
-        <is>
-          <t>2025-03-20 21:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1061" t="inlineStr">
-        <is>
-          <t>15-Year Mortgage RateMAR/20</t>
-        </is>
-      </c>
-      <c r="C1061" t="inlineStr"/>
-      <c r="D1061" t="inlineStr"/>
-      <c r="E1061" t="inlineStr"/>
-      <c r="F1061" t="inlineStr"/>
-      <c r="G1061" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1062">
-      <c r="A1062" t="inlineStr">
-        <is>
-          <t>2025-03-20 21:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1062" t="inlineStr">
-        <is>
-          <t>30-Year Mortgage RateMAR/20</t>
-        </is>
-      </c>
-      <c r="C1062" t="inlineStr"/>
-      <c r="D1062" t="inlineStr"/>
-      <c r="E1062" t="inlineStr"/>
-      <c r="F1062" t="inlineStr"/>
-      <c r="G1062" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1063">
-      <c r="A1063" t="inlineStr">
-        <is>
-          <t>2025-03-20 22:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1063" t="inlineStr">
-        <is>
-          <t>10-Year TIPS Auction</t>
-        </is>
-      </c>
-      <c r="C1063" t="inlineStr"/>
-      <c r="D1063" t="inlineStr">
-        <is>
-          <t>2.243%</t>
-        </is>
-      </c>
-      <c r="E1063" t="inlineStr"/>
-      <c r="F1063" t="inlineStr"/>
-      <c r="G1063" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1064">
-      <c r="A1064" t="inlineStr">
-        <is>
-          <t>2025-03-21 02:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1064" t="inlineStr">
-        <is>
-          <t>Fed Balance SheetMAR/19</t>
-        </is>
-      </c>
-      <c r="C1064" t="inlineStr"/>
-      <c r="D1064" t="inlineStr"/>
-      <c r="E1064" t="inlineStr"/>
-      <c r="F1064" t="inlineStr"/>
-      <c r="G1064" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1065">
-      <c r="A1065" t="inlineStr">
-        <is>
-          <t>2025-03-21 22:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1065" t="inlineStr">
-        <is>
-          <t>Baker Hughes Oil Rig CountMAR/21</t>
-        </is>
-      </c>
-      <c r="C1065" t="inlineStr"/>
-      <c r="D1065" t="inlineStr"/>
-      <c r="E1065" t="inlineStr"/>
-      <c r="F1065" t="inlineStr"/>
-      <c r="G1065" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1066">
-      <c r="A1066" t="inlineStr">
-        <is>
-          <t>2025-03-21 22:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1066" t="inlineStr">
-        <is>
-          <t>Baker Hughes Total Rigs CountMAR/21</t>
-        </is>
-      </c>
-      <c r="C1066" t="inlineStr"/>
-      <c r="D1066" t="inlineStr"/>
-      <c r="E1066" t="inlineStr"/>
-      <c r="F1066" t="inlineStr"/>
-      <c r="G1066" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1067">
-      <c r="A1067" t="inlineStr">
-        <is>
-          <t>2025-03-24 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B1067" t="inlineStr">
-        <is>
-          <t>Chicago Fed National Activity IndexFEB</t>
-        </is>
-      </c>
-      <c r="C1067" t="inlineStr"/>
-      <c r="D1067" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="E1067" t="inlineStr"/>
-      <c r="F1067" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
-      <c r="G1067" t="n">
         <v>2</v>
       </c>
     </row>
